--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JV22853121</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>000000108501648938</t>
+          <t>0000VG17072025QA76140000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,20 +554,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>340225-021-MISC</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:20.045</t>
+          <t>2025-07-17T21:04:22.226</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -575,20 +575,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>24</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JV54629393</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -603,7 +633,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>000000106139893139</t>
+          <t>0000VG17072025QA18580001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -613,20 +643,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>112308-011-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:21.491</t>
+          <t>2025-07-17T21:04:22.233</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,20 +664,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JV64183602</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -662,7 +722,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>000000108802883491</t>
+          <t>0000VG17072025QA27220002</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -672,20 +732,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>112308-011-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:24.253</t>
+          <t>2025-07-17T21:04:22.234</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -693,20 +753,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>24</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JV64183602</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -721,7 +811,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>000000108802883491</t>
+          <t>0000VG17072025QA80720003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -731,20 +821,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>112308-011-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:24.255</t>
+          <t>2025-07-17T21:04:22.235</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -752,20 +842,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JV64183602</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -780,7 +900,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>000000108802883491</t>
+          <t>0000VG17072025QA27120004</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -790,20 +910,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>112308-011-XL</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:24.257</t>
+          <t>2025-07-17T21:04:22.235</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -811,20 +931,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>24</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JV65651617</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,7 +989,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>000000101992884812</t>
+          <t>0000VG17072025QA51610005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -849,20 +999,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104265-054-9</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:16.299</t>
+          <t>2025-07-17T21:04:16.447</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -870,20 +1020,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JV68655791</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,7 +1078,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>000000109272629830</t>
+          <t>0000VG17072025QA95050006</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -908,20 +1088,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DA1746-258-MISC</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:22.846</t>
+          <t>2025-07-17T21:04:16.453</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -929,20 +1109,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JV68655791</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -957,7 +1167,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>000000109272629830</t>
+          <t>0000VG17072025QA81350007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -967,20 +1177,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DA1746-258-MISC</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:22.847</t>
+          <t>2025-07-17T21:04:16.453</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -988,20 +1198,50 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>24</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JV68655791</t>
+          <t>VASN1707QA5060</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,7 +1256,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>000000109272629830</t>
+          <t>0000VG17072025QA60090008</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1026,20 +1266,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DA1746-258-MISC</t>
+          <t>420420-420-M</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>JVENKI</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2025-07-15T15:38:22.849</t>
+          <t>2025-07-17T21:04:16.454</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1047,15 +1287,1914 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VASN1707QA5060</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA12260009</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:16.454</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VASN1707QA5060</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA89050010</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.426</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VASN1707QA5060</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA31840011</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.436</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VASN1707QA5060</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA66890012</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.437</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>24</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VASN1707QA5060</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA83900013</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.437</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VASN1707QA5060</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA20970014</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.437</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>BOLQA07172582</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PROQA07172582</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>24</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>TRLQA07172582</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA98670015</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:22.235</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA75830016</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:22.235</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>24</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>12</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA29240017</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:22.235</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>24</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA33920018</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:22.235</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA75940019</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:22.236</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>24</v>
+      </c>
+      <c r="P21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>12</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA36890020</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:16.454</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>24</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>12</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA49070021</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:16.454</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA33010022</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:16.454</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>12</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA79000023</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:16.454</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P25" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>12</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA78020024</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>420420-420-M</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:16.454</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>24</v>
+      </c>
+      <c r="P26" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>12</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA41630025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.437</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>24</v>
+      </c>
+      <c r="P27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>12</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA51030026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.438</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>12</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA13970027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.438</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>24</v>
+      </c>
+      <c r="P29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>12</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA75370028</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.438</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>24</v>
+      </c>
+      <c r="P30" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VASN1707QA8841</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0000VG17072025QA72270029</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:04:19.438</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>BOLQA07172588</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PROQA07172588</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>24</v>
+      </c>
+      <c r="P31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>12</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>TRLQA07172588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1081,19 +3220,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{
+          <t xml:space="preserve">{
     "Messages": null,
-    "CreatedTimestamp": "2025-07-15T15:38:22.843",
+    "CreatedTimestamp": "2025-07-17T20:43:17.513",
     "AsnRequestedService": [],
-    "EstimatedWeight": 0.0,
+    "EstimatedWeight": 110.0,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
-        "ProNumber": null,
+        "ProNumber": "PROQA07172588",
         "ShipmentStart": null,
         "ShipToCustomerName": null,
-        "ExpediteFlag": false,
-        "SealNumber": null,
+        "ExpediteFlag": true,
+        "SealNumber": "SLQA07172588",
         "MinimumLPNStatus": null,
         "SoldToCustomerName": null,
         "Digital": null,
@@ -1101,25 +3240,25 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": null,
+        "BolNumber": "BOLQA07172588",
         "ShipmentCreateDate": null,
         "SalesOrderType": null
     },
-    "Process": "AsnHeaderMetricsService",
-    "ProNumber": null,
+    "Process": "AsnStatusUpdate",
+    "ProNumber": "PROQA07172588",
     "DestinationFacilityAliasId": null,
-    "UpdatedBy": "JVENKI",
+    "UpdatedBy": "vgana3",
     "AsnLine": [],
     "EstimatedReceiptDate": null,
     "PurgeDate": null,
     "ReferenceShipmentId": null,
-    "CreatedBy": "JVENKI",
+    "CreatedBy": "vgana3",
     "VerificationAttempted": false,
     "BusinessUnitId": null,
-    "PreDeterminedLpnCount": 1.0,
+    "PreDeterminedLpnCount": 15.0,
     "AsnVerificationDate": null,
-    "PreReceiptStatusId": null,
-    "ContextId": "1575ec53fd77e5e5::6c50d308a031939c",
+    "PreReceiptStatusId": "3",
+    "ContextId": "9c5337ace8029ee3::21ec2ec98ec82575",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
@@ -1127,40 +3266,40 @@
     "VendorId": null,
     "ShippedDate": null,
     "AsnStatus": "1000",
-    "BillOfLadingNumber": null,
+    "BillOfLadingNumber": "BOLQA07172588",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-07-15T15:38:22.845",
+            "CreatedTimestamp": "2025-07-17T20:43:17.515",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "EstimatedWeight": null,
             "FinalDestinationFacilityId": null,
             "VendorId": null,
             "Extended": {
-                "LpnLength": null,
-                "LpnHeight": null,
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
                 "DestinationFacilityId": null,
-                "LpnWidth": null
+                "LpnWidth": 12.0
             },
-            "DiversionCodeId": null,
-            "Process": "/asn/save",
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
             "ItemAttributesValidated": true,
-            "UpdatedBy": "JVENKI",
+            "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
             "PurgeDate": null,
             "FinalDestinationAddress": null,
-            "LpnSizeTypeId": null,
+            "LpnSizeTypeId": "CARTON",
             "FacilityTimezone": "Japan",
             "Asn": {
-                "AsnId": "JV68655791"
+                "AsnId": "VASN1707QA8841"
             },
-            "AsnId": "JV68655791",
-            "UpdatedTimestamp": "2025-07-15T15:38:23.057",
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:22.13",
             "MarkFor": null,
-            "CreatedBy": "JVENKI",
+            "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "AllocationTypeId": null,
-            "LpnId": "000000109272629830",
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA98670015",
             "BusinessUnitId": null,
             "LpnStatus": "1000",
             "LocationId": null,
@@ -1169,7 +3308,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-15T15:38:22.846",
+                    "CreatedTimestamp": "2025-07-17T20:43:17.517",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -1177,11 +3316,11 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
+                    "Process": "PreReceiptResponseProcessingService",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "DA1746-258-MISC",
-                    "UpdatedBy": "JVENKI",
+                    "ItemId": "924156-100-S",
+                    "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
@@ -1189,25 +3328,25 @@
                     "PurgeDate": null,
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
-                    "CreatedBy": "JVENKI",
+                    "CreatedBy": "vgana3",
                     "BatchNumber": null,
                     "BusinessUnitId": null,
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
-                    "PurchaseOrderId": "",
-                    "ContextId": "1575ec53fd77e5e5::10f5546c89bc9800",
-                    "LpnDetailId": "ecb10c9b-d212-4797-b7d1-049c96252c67",
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+                    "LpnDetailId": "a12f719b-52d3-4b42-82dc-64096856c4e0",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7525939028457155352
+                        "PK": 7527849975151703896
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
-                    "ManufacturingDate": "2025-06-25",
+                    "ManufacturingDate": null,
                     "Style": null,
                     "ProductClass": null,
                     "Season": null,
@@ -1215,22 +3354,75 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-15T15:38:22.846",
-                    "PrereceiptAllocatedQuantity": null,
+                    "UpdatedTimestamp": "2025-07-17T21:04:22.235",
+                    "PrereceiptAllocatedQuantity": 0.0,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 1.0,
+                    "ShippedQuantity": 10.0,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7525939028457167634",
-                    "Unique_Identifier": "7525939028457167634__ecb10c9b-d212-4797-b7d1-049c96252c67"
-                },
+                    "PK": "7527849975171716717",
+                    "Unique_Identifier": "7527849975171716717__a12f719b-52d3-4b42-82dc-64096856c4e0"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "PreReceiptStatusId": "3",
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+            "Canceled": false,
+            "PK": "7527849975151703896",
+            "Unique_Identifier": "7527849975151703896__0000VG17072025QA98670015",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-07-17T20:43:17.519",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "EstimatedWeight": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "PurgeDate": null,
+            "FinalDestinationAddress": null,
+            "LpnSizeTypeId": "CARTON",
+            "FacilityTimezone": "Japan",
+            "Asn": {
+                "AsnId": "VASN1707QA8841"
+            },
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:22.138",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA75830016",
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-15T15:38:22.847",
+                    "CreatedTimestamp": "2025-07-17T20:43:17.52",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -1238,11 +3430,11 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
+                    "Process": "PreReceiptResponseProcessingService",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "DA1746-258-MISC",
-                    "UpdatedBy": "JVENKI",
+                    "ItemId": "924156-100-S",
+                    "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
@@ -1250,25 +3442,25 @@
                     "PurgeDate": null,
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
-                    "CreatedBy": "JVENKI",
+                    "CreatedBy": "vgana3",
                     "BatchNumber": null,
                     "BusinessUnitId": null,
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
-                    "PurchaseOrderId": "",
-                    "ContextId": "1575ec53fd77e5e5::10f5546c89bc9800",
-                    "LpnDetailId": "6455b6ad-8671-4c3a-b5bf-dda44f6364aa",
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+                    "LpnDetailId": "64bff08e-3f2e-42dc-bf91-4b1eb3ee588e",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7525939028457155352
+                        "PK": 7527849975191724249
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
-                    "ManufacturingDate": "2025-06-25",
+                    "ManufacturingDate": null,
                     "Style": null,
                     "ProductClass": null,
                     "Season": null,
@@ -1276,22 +3468,75 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-15T15:38:22.847",
-                    "PrereceiptAllocatedQuantity": null,
+                    "UpdatedTimestamp": "2025-07-17T21:04:22.235",
+                    "PrereceiptAllocatedQuantity": 0.0,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 1.0,
+                    "ShippedQuantity": 10.0,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7525939028477176777",
-                    "Unique_Identifier": "7525939028477176777__6455b6ad-8671-4c3a-b5bf-dda44f6364aa"
-                },
+                    "PK": "7527849975201735232",
+                    "Unique_Identifier": "7527849975201735232__64bff08e-3f2e-42dc-bf91-4b1eb3ee588e"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "PreReceiptStatusId": "3",
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+            "Canceled": false,
+            "PK": "7527849975191724249",
+            "Unique_Identifier": "7527849975191724249__0000VG17072025QA75830016",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-07-17T20:43:17.522",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "EstimatedWeight": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "PurgeDate": null,
+            "FinalDestinationAddress": null,
+            "LpnSizeTypeId": "CARTON",
+            "FacilityTimezone": "Japan",
+            "Asn": {
+                "AsnId": "VASN1707QA8841"
+            },
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:22.146",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA29240017",
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-15T15:38:22.849",
+                    "CreatedTimestamp": "2025-07-17T20:43:17.523",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -1299,11 +3544,11 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
+                    "Process": "PreReceiptResponseProcessingService",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "DA1746-258-MISC",
-                    "UpdatedBy": "JVENKI",
+                    "ItemId": "924156-100-S",
+                    "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
@@ -1311,25 +3556,25 @@
                     "PurgeDate": null,
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
-                    "CreatedBy": "JVENKI",
+                    "CreatedBy": "vgana3",
                     "BatchNumber": null,
                     "BusinessUnitId": null,
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
-                    "PurchaseOrderId": "",
-                    "ContextId": "1575ec53fd77e5e5::10f5546c89bc9800",
-                    "LpnDetailId": "9648a41c-08a6-423d-88f2-4009fff61829",
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+                    "LpnDetailId": "d1d361a5-ec6c-4ceb-8ee9-2d758742a4b2",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7525939028457155352
+                        "PK": 7527849975211748300
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
-                    "ManufacturingDate": "2025-06-25",
+                    "ManufacturingDate": null,
                     "Style": null,
                     "ProductClass": null,
                     "Season": null,
@@ -1337,17 +3582,17 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-15T15:38:22.849",
-                    "PrereceiptAllocatedQuantity": null,
+                    "UpdatedTimestamp": "2025-07-17T21:04:22.235",
+                    "PrereceiptAllocatedQuantity": 0.0,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 1.0,
+                    "ShippedQuantity": 10.0,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7525939028487185240",
-                    "Unique_Identifier": "7525939028487185240__9648a41c-08a6-423d-88f2-4009fff61829"
+                    "PK": "7527849975231752900",
+                    "Unique_Identifier": "7527849975231752900__d1d361a5-ec6c-4ceb-8ee9-2d758742a4b2"
                 }
             ],
             "EntityLabels": null,
@@ -1355,41 +3600,421 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": null,
-            "PreReceiptStatusId": null,
+            "PreReceiptStatusId": "3",
             "SingleItemLpn": true,
-            "PurchaseOrderId": null,
-            "ContextId": "1575ec53fd77e5e5::10f5546c89bc9800",
+            "PurchaseOrderId": "25050501",
+            "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
             "Canceled": false,
-            "PK": "7525939028457155352",
-            "Unique_Identifier": "7525939028457155352__000000109272629830",
+            "PK": "7527849975211748300",
+            "Unique_Identifier": "7527849975211748300__0000VG17072025QA29240017",
             "DimensionUomId": null,
             "EstimationGroupId": null
-        }
-    ],
-    "TrailerId": null,
-    "FirstReceiptDate": null,
-    "LastReceiptDate": null,
-    "CarrierId": null,
-    "ShippedLpns": 1.0,
-    "EstimatedVolume": 0.0,
-    "OriginFacilityId": null,
-    "FacilityTimezone": "Japan",
-    "AsnId": "JV68655791",
-    "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-07-15T15:38:37.409",
-    "ReportingReceiptTypeId": null,
-    "ShipmentAsnAssociation": [],
-    "EstimatedDeliveryDate": null,
-    "ReceivedLpns": 0.0,
-    "EntityLabels": null,
-    "RrnId": null,
-    "OrgId": "1081",
-    "FacilityId": "1081",
-    "ExternalOrgId": null,
-    "PK": "7525939028437142134",
-    "ReceivingCompleted": false,
-    "Unique_Identifier": "7525939028437142134__JV68655791"
-}</t>
+        },
+        {
+            "CreatedTimestamp": "2025-07-17T20:43:17.524",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "EstimatedWeight": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "PurgeDate": null,
+            "FinalDestinationAddress": null,
+            "LpnSizeTypeId": "CARTON",
+            "FacilityTimezone": "Japan",
+            "Asn": {
+                "AsnId": "VASN1707QA8841"
+            },
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:22.153",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA33920018",
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
+                {
+                    "ExpiryDate": null,
+                    "RetailPrice": null,
+                    "CreatedTimestamp": "2025-07-17T20:43:17.525",
+                    "Extended": {
+                        "CutNumber": null,
+                        "PurchaseOrderItemId": null,
+                        "UnitOfMeasureCode": null,
+                        "DeliveryNoteItemNumber": null
+                    },
+                    "CountryOfOrigin": "CN",
+                    "Process": "PreReceiptResponseProcessingService",
+                    "AsnLineId": null,
+                    "InventoryTypeId": null,
+                    "ItemId": "924156-100-S",
+                    "UpdatedBy": "vgana3",
+                    "InventoryAttribute1": "01000",
+                    "InventoryAttribute2": null,
+                    "InventoryAttribute3": null,
+                    "InventoryAttribute4": null,
+                    "PurgeDate": null,
+                    "InventoryAttribute5": null,
+                    "PurchaseOrderLineId": "",
+                    "CreatedBy": "vgana3",
+                    "BatchNumber": null,
+                    "BusinessUnitId": null,
+                    "StandardPackQuantity": null,
+                    "ExternalOrderId": null,
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+                    "LpnDetailId": "33427a07-be58-48dc-b85a-f6823bb4b305",
+                    "OriginalShippingFacilityId": null,
+                    "StandardSubPackQuantity": null,
+                    "VendorId": null,
+                    "ExternalOrderLineId": null,
+                    "LpnDetailStatus": "1000",
+                    "Lpn": {
+                        "PK": 7527849975241768297
+                    },
+                    "QuantityUomId": "LPN",
+                    "SeasonYear": null,
+                    "ManufacturingDate": null,
+                    "Style": null,
+                    "ProductClass": null,
+                    "Season": null,
+                    "CrossReferenceOrderId": null,
+                    "HandlingUomQuantity": null,
+                    "TierQuantity": null,
+                    "CrossReferenceOrderLineId": null,
+                    "UpdatedTimestamp": "2025-07-17T21:04:22.235",
+                    "PrereceiptAllocatedQuantity": 0.0,
+                    "LpnDetailAttribute": [],
+                    "LpnDetailGroupingId": null,
+                    "ShippedQuantity": 10.0,
+                    "EntityLabels": null,
+                    "ProductStatusId": null,
+                    "OrgId": "1081",
+                    "FacilityId": "1081",
+                    "PK": "7527849975251776059",
+                    "Unique_Identifier": "7527849975251776059__33427a07-be58-48dc-b85a-f6823bb4b305"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "PreReceiptStatusId": "3",
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+            "Canceled": false,
+            "PK": "7527849975241768297",
+            "Unique_Identifier": "7527849975241768297__0000VG17072025QA33920018",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-07-17T20:43:17.526",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "EstimatedWeight": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "PurgeDate": null,
+            "FinalDestinationAddress": null,
+            "LpnSizeTypeId": "CARTON",
+            "FacilityTimezone": "Japan",
+            "Asn": {
+                "AsnId": "VASN1707QA8841"
+            },
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:22.16",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA75940019",
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
+                {
+                    "ExpiryDate": null,
+                    "RetailPrice": null,
+                    "CreatedTimestamp": "2025-07-17T20:43:17.527",
+                    "Extended": {
+                        "CutNumber": null,
+                        "PurchaseOrderItemId": null,
+                        "UnitOfMeasureCode": null,
+                        "DeliveryNoteItemNumber": null
+                    },
+                    "CountryOfOrigin": "CN",
+                    "Process": "PreReceiptResponseProcessingService",
+                    "AsnLineId": null,
+                    "InventoryTypeId": null,
+                    "ItemId": "924156-100-S",
+                    "UpdatedBy": "vgana3",
+                    "InventoryAttribute1": "01000",
+                    "InventoryAttribute2": null,
+                    "InventoryAttribute3": null,
+                    "InventoryAttribute4": null,
+                    "PurgeDate": null,
+                    "InventoryAttribute5": null,
+                    "PurchaseOrderLineId": "",
+                    "CreatedBy": "vgana3",
+                    "BatchNumber": null,
+                    "BusinessUnitId": null,
+                    "StandardPackQuantity": null,
+                    "ExternalOrderId": null,
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+                    "LpnDetailId": "7677c7b4-6134-4ac4-ae2c-4b8afefe99cd",
+                    "OriginalShippingFacilityId": null,
+                    "StandardSubPackQuantity": null,
+                    "VendorId": null,
+                    "ExternalOrderLineId": null,
+                    "LpnDetailStatus": "1000",
+                    "Lpn": {
+                        "PK": 7527849975261781586
+                    },
+                    "QuantityUomId": "LPN",
+                    "SeasonYear": null,
+                    "ManufacturingDate": null,
+                    "Style": null,
+                    "ProductClass": null,
+                    "Season": null,
+                    "CrossReferenceOrderId": null,
+                    "HandlingUomQuantity": null,
+                    "TierQuantity": null,
+                    "CrossReferenceOrderLineId": null,
+                    "UpdatedTimestamp": "2025-07-17T21:04:22.236",
+                    "PrereceiptAllocatedQuantity": 0.0,
+                    "LpnDetailAttribute": [],
+                    "LpnDetailGroupingId": null,
+                    "ShippedQuantity": 10.0,
+                    "EntityLabels": null,
+                    "ProductStatusId": null,
+                    "OrgId": "1081",
+                    "FacilityId": "1081",
+                    "PK": "7527849975271791069",
+                    "Unique_Identifier": "7527849975271791069__7677c7b4-6134-4ac4-ae2c-4b8afefe99cd"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "PreReceiptStatusId": "3",
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "9c5337ace8029ee3::b7d502fd0bbfe278",
+            "Canceled": false,
+            "PK": "7527849975261781586",
+            "Unique_Identifier": "7527849975261781586__0000VG17072025QA75940019",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-07-17T20:43:17.528",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "EstimatedWeight": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "PurgeDate": null,
+            "FinalDestinationAddress": null,
+            "LpnSizeTypeId": "CARTON",
+            "FacilityTimezone": "Japan",
+            "Asn": {
+                "AsnId": "VASN1707QA8841"
+            },
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:16.343",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA36890020",
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
+                {
+                    "ExpiryDate": null,
+                    "RetailPrice": null,
+                    "CreatedTimestamp": "2025-07-17T20:43:17.529",
+                    "Extended": {
+                        "CutNumber": null,
+                        "PurchaseOrderItemId": null,
+                        "UnitOfMeasureCode": null,
+                        "DeliveryNoteItemNumber": null
+                    },
+                    "CountryOfOrigin": "CN",
+                    "Process": "PreReceiptResponseProcessingService",
+                    "AsnLineId": null,
+                    "InventoryTypeId": null,
+                    "ItemId": "420420-420-M",
+                    "UpdatedBy": "vgana3",
+                    "InventoryAttribute1": "01000",
+                    "InventoryAttribute2": null,
+                    "InventoryAttribute3": null,
+                    "InventoryAttribute4": null,
+                    "PurgeDate": null,
+                    "InventoryAttribute5": null,
+                    "PurchaseOrderLineId": "",
+                    "CreatedBy": "vgana3",
+                    "BatchNumber": null,
+                    "BusinessUnitId": null,
+                    "StandardPackQuantity": null,
+                    "ExternalOrderId": null,
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "9c5337ace8029ee3::45bd5774ad245733",
+                    "LpnDetailId": "78b2a9f7-706a-4a0f-8f99-2975d214bb2f",
+                    "OriginalShippingFacilityId": null,
+                    "StandardSubPackQuantity": null,
+                    "VendorId": null,
+                    "ExternalOrderLineId": null,
+                    "LpnDetailStatus": "1000",
+                    "Lpn": {
+                        "PK": 7527849975281808599
+                    },
+                    "QuantityUomId": "LPN",
+                    "SeasonYear": null,
+                    "ManufacturingDate": null,
+                    "Style": null,
+                    "ProductClass": null,
+                    "Season": null,
+                    "CrossReferenceOrderId": null,
+                    "HandlingUomQuantity": null,
+                    "TierQuantity": null,
+                    "CrossReferenceOrderLineId": null,
+                    "UpdatedTimestamp": "2025-07-17T21:04:16.454",
+                    "PrereceiptAllocatedQuantity": 0.0,
+                    "LpnDetailAttribute": [],
+                    "LpnDetailGroupingId": null,
+                    "ShippedQuantity": 10.0,
+                    "EntityLabels": null,
+                    "ProductStatusId": null,
+                    "OrgId": "1081",
+                    "FacilityId": "1081",
+                    "PK": "7527849975291814896",
+                    "Unique_Identifier": "7527849975291814896__78b2a9f7-706a-4a0f-8f99-2975d214bb2f"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "PreReceiptStatusId": "3",
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "9c5337ace8029ee3::45bd5774ad245733",
+            "Canceled": false,
+            "PK": "7527849975281808599",
+            "Unique_Identifier": "7527849975281808599__0000VG17072025QA36890020",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-07-17T20:43:17.53",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "EstimatedWeight": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": "STORAGE",
+            "Process": "PreReceiptResponseProcessingService",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "PurgeDate": null,
+            "FinalDestinationAddress": null,
+            "LpnSizeTypeId": "CARTON",
+            "FacilityTimezone": "Japan",
+            "Asn": {
+                "AsnId": "VASN1707QA8841"
+            },
+            "AsnId": "VASN1707QA8841",
+            "UpdatedTimestamp": "2025-07-17T21:04:16.352",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "0000VG17072025QA49070021",
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
+                {
+                    "ExpiryDate": null,
+                    "RetailPrice": null,
+                    "CreatedTimestamp": "2025-07-17T20:43:17.531",
+                    "Extended": {
+                        "CutNumber": null,
+                        "PurchaseOrderItemId": null,
+                        "UnitOfMeasureCode": null,
+                        "DeliveryNoteItemNumber": null
+                    },
+                    "CountryOfOrigin": "CN",
+                    "Process": "PreReceiptResponseProcessingService",
+                    "AsnLineId": null,
+                    "InventoryTypeId": null,
+                    "ItemId": "420420-420-M",
+                    "UpdatedBy": "vgana3",
+                    "InventoryAttribute1": "01000",
+                    "InventoryAttribute2": null,
+                    "InventoryAttribute3": null,
+                    "InventoryAttribute4": null,
+                    "PurgeDate": null,
+                    "InventoryAttribute5": null,
+                    "PurchaseOrderLineId": "",
+                    "CreatedBy": "vgana3",
+                    "BatchNumber": null,
+      </t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,12 +539,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VGASN2107QA9450</t>
+          <t>VGASN0722QA4571</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0000VG07212025QA51680000</t>
+          <t>0000VG07222025QA49200002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -585,12 +585,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BOLQA07212560</t>
+          <t>BOLQA07222545</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PROQA07212560</t>
+          <t>PROQA07222545</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TRLQA07212560</t>
+          <t>TRLQA07222545</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -629,19 +629,19 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-07-22T00:45:13.524</t>
+          <t>2025-07-22T21:17:34.423</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VGASN2107QA9450</t>
+          <t>VGASN0722QA4571</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0000VG07212025QA81720001</t>
+          <t>0000VG07222025QA20210003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -682,12 +682,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BOLQA07212560</t>
+          <t>BOLQA07222545</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PROQA07212560</t>
+          <t>PROQA07222545</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>TRLQA07212560</t>
+          <t>TRLQA07222545</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -726,7 +726,201 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-07-22T00:45:13.527</t>
+          <t>2025-07-22T21:17:34.424</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VGASN0722QA6520</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0000VG07222025QA43750000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BOLQA07222579</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PROQA07222579</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>24</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>TRLQA07222579</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2025-07-22T21:17:34.412</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VGASN0722QA6520</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0000VG07222025QA14210001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BOLQA07222579</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PROQA07222579</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>CARTON</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>TRLQA07222579</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2025-07-22T21:17:34.422</t>
         </is>
       </c>
     </row>
@@ -756,17 +950,17 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-07-22T00:35:58.734",
+    "CreatedTimestamp": "2025-07-22T21:16:26.09",
     "AsnRequestedService": [],
     "EstimatedWeight": 4.8,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
-        "ProNumber": "PROQA07212560",
+        "ProNumber": "PROQA07222579",
         "ShipmentStart": null,
         "ShipToCustomerName": null,
         "ExpediteFlag": false,
-        "SealNumber": "SLQA07212560",
+        "SealNumber": "SLQA07222579",
         "MinimumLPNStatus": null,
         "SoldToCustomerName": null,
         "Digital": null,
@@ -774,36 +968,36 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": "BOLQA07212560",
+        "BolNumber": "BOLQA07222579",
         "ShipmentCreateDate": null,
         "SalesOrderType": null
     },
-    "Process": "AsnPurgeService",
-    "ProNumber": "PROQA07212560",
+    "Process": "AsnStatusUpdate",
+    "ProNumber": "PROQA07222579",
     "DestinationFacilityAliasId": null,
     "UpdatedBy": "vgana3",
     "AsnLine": [],
     "EstimatedReceiptDate": null,
-    "PurgeDate": "2025-10-20T00:45:13.503",
+    "PurgeDate": null,
     "ReferenceShipmentId": null,
     "CreatedBy": "vgana3",
-    "VerificationAttempted": true,
+    "VerificationAttempted": false,
     "BusinessUnitId": null,
     "PreDeterminedLpnCount": 2.0,
-    "AsnVerificationDate": "2025-07-22T00:45:13.161",
-    "PreReceiptStatusId": "4",
-    "ContextId": "f38c7131d1978605::2b3d2670eaa481",
+    "AsnVerificationDate": null,
+    "PreReceiptStatusId": "3",
+    "ContextId": "a659db5148b4dbd8::8c8ec38e191c5875",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
     "OriginFacilityAliasId": null,
     "VendorId": null,
     "ShippedDate": null,
-    "AsnStatus": "8000",
-    "BillOfLadingNumber": "BOLQA07212560",
+    "AsnStatus": "1000",
+    "BillOfLadingNumber": "BOLQA07222579",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-07-22T00:35:58.736",
+            "CreatedTimestamp": "2025-07-22T21:16:26.189",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "EstimatedWeight": null,
@@ -816,33 +1010,33 @@
                 "LpnWidth": 12.0
             },
             "DiversionCodeId": "STORAGE",
-            "Process": "AsnPurgeService",
+            "Process": "PreReceiptResponseProcessingService",
             "ItemAttributesValidated": true,
             "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
-            "PurgeDate": "2025-10-20T00:45:13.503",
+            "PurgeDate": null,
             "FinalDestinationAddress": null,
             "LpnSizeTypeId": "CARTON",
             "FacilityTimezone": "Japan",
             "Asn": {
-                "AsnId": "VGASN2107QA9450"
+                "AsnId": "VGASN0722QA6520"
             },
-            "AsnId": "VGASN2107QA9450",
-            "UpdatedTimestamp": "2025-07-22T00:45:13.523",
+            "AsnId": "VGASN0722QA6520",
+            "UpdatedTimestamp": "2025-07-22T21:17:34.233",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
             "AllocationTypeId": "ProcessNeed",
-            "LpnId": "0000VG07212025QA51680000",
+            "LpnId": "0000VG07222025QA43750000",
             "BusinessUnitId": null,
-            "LpnStatus": "4000",
+            "LpnStatus": "1000",
             "LocationId": null,
             "LpnTypeId": "ILPN",
             "LpnDetail": [
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-22T00:35:58.738",
+                    "CreatedTimestamp": "2025-07-22T21:16:26.256",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -850,7 +1044,7 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "AsnPurgeService",
+                    "Process": "PreReceiptResponseProcessingService",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
                     "ItemId": "DD9293-100-7",
@@ -859,7 +1053,7 @@
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
                     "InventoryAttribute4": null,
-                    "PurgeDate": "2025-10-20T00:45:13.503",
+                    "PurgeDate": null,
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
                     "CreatedBy": "vgana3",
@@ -868,15 +1062,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "f38c7131d1978605::2b3d2670eaa481",
-                    "LpnDetailId": "402a29b4-6d8e-4cc4-aef0-8b7ecbcc42c3",
+                    "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
+                    "LpnDetailId": "f1acce19-744c-4ea2-809c-2381ae2067bd",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7531445587368665843
+                        "PK": 7532189861886301493
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -888,7 +1082,7 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-22T00:45:13.524",
+                    "UpdatedTimestamp": "2025-07-22T21:17:34.412",
                     "PrereceiptAllocatedQuantity": 0.0,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
@@ -897,8 +1091,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7531445587388678732",
-                    "Unique_Identifier": "7531445587388678732__402a29b4-6d8e-4cc4-aef0-8b7ecbcc42c3"
+                    "PK": "7532189862556319133",
+                    "Unique_Identifier": "7532189862556319133__f1acce19-744c-4ea2-809c-2381ae2067bd"
                 }
             ],
             "EntityLabels": null,
@@ -906,18 +1100,18 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": null,
-            "PreReceiptStatusId": "4",
+            "PreReceiptStatusId": "3",
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "f38c7131d1978605::2b3d2670eaa481",
+            "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
             "Canceled": false,
-            "PK": "7531445587368665843",
-            "Unique_Identifier": "7531445587368665843__0000VG07212025QA51680000",
+            "PK": "7532189861886301493",
+            "Unique_Identifier": "7532189861886301493__0000VG07222025QA43750000",
             "DimensionUomId": null,
             "EstimationGroupId": null
         },
         {
-            "CreatedTimestamp": "2025-07-22T00:35:58.74",
+            "CreatedTimestamp": "2025-07-22T21:16:26.306",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "EstimatedWeight": null,
@@ -930,33 +1124,33 @@
                 "LpnWidth": 12.0
             },
             "DiversionCodeId": "STORAGE",
-            "Process": "AsnPurgeService",
+            "Process": "PreReceiptResponseProcessingService",
             "ItemAttributesValidated": true,
             "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
-            "PurgeDate": "2025-10-20T00:45:13.503",
+            "PurgeDate": null,
             "FinalDestinationAddress": null,
             "LpnSizeTypeId": "CARTON",
             "FacilityTimezone": "Japan",
             "Asn": {
-                "AsnId": "VGASN2107QA9450"
+                "AsnId": "VGASN0722QA6520"
             },
-            "AsnId": "VGASN2107QA9450",
-            "UpdatedTimestamp": "2025-07-22T00:45:13.524",
+            "AsnId": "VGASN0722QA6520",
+            "UpdatedTimestamp": "2025-07-22T21:17:34.258",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
             "AllocationTypeId": "ProcessNeed",
-            "LpnId": "0000VG07212025QA81720001",
+            "LpnId": "0000VG07222025QA14210001",
             "BusinessUnitId": null,
-            "LpnStatus": "4000",
+            "LpnStatus": "1000",
             "LocationId": null,
             "LpnTypeId": "ILPN",
             "LpnDetail": [
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-22T00:35:58.743",
+                    "CreatedTimestamp": "2025-07-22T21:16:26.308",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -964,7 +1158,7 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "AsnPurgeService",
+                    "Process": "PreReceiptResponseProcessingService",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
                     "ItemId": "DD9293-100-7",
@@ -973,7 +1167,7 @@
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
                     "InventoryAttribute4": null,
-                    "PurgeDate": "2025-10-20T00:45:13.503",
+                    "PurgeDate": null,
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
                     "CreatedBy": "vgana3",
@@ -982,15 +1176,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "f38c7131d1978605::2b3d2670eaa481",
-                    "LpnDetailId": "f2bad036-0924-4613-8963-e9be751364fd",
+                    "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
+                    "LpnDetailId": "b658053a-818a-433a-a8a6-d05d07bb304d",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7531445587408685430
+                        "PK": 7532189863066328041
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -1002,7 +1196,7 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-22T00:45:13.527",
+                    "UpdatedTimestamp": "2025-07-22T21:17:34.422",
                     "PrereceiptAllocatedQuantity": 0.0,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
@@ -1011,8 +1205,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7531445587438691506",
-                    "Unique_Identifier": "7531445587438691506__f2bad036-0924-4613-8963-e9be751364fd"
+                    "PK": "7532189863086332237",
+                    "Unique_Identifier": "7532189863086332237__b658053a-818a-433a-a8a6-d05d07bb304d"
                 }
             ],
             "EntityLabels": null,
@@ -1020,60 +1214,60 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": null,
-            "PreReceiptStatusId": "4",
+            "PreReceiptStatusId": "3",
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "f38c7131d1978605::2b3d2670eaa481",
+            "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
             "Canceled": false,
-            "PK": "7531445587408685430",
-            "Unique_Identifier": "7531445587408685430__0000VG07212025QA81720001",
+            "PK": "7532189863066328041",
+            "Unique_Identifier": "7532189863066328041__0000VG07222025QA14210001",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA07212560",
-    "FirstReceiptDate": "2025-07-22T00:38:29.693",
-    "LastReceiptDate": "2025-07-22T00:38:55.248",
+    "TrailerId": "TRLQA07222579",
+    "FirstReceiptDate": null,
+    "LastReceiptDate": null,
     "CarrierId": "AUPU",
     "ShippedLpns": 2.0,
     "EstimatedVolume": 56628.0,
     "OriginFacilityId": "0005005401",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN2107QA9450",
+    "AsnId": "VGASN0722QA6520",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-07-22T00:45:13.507",
+    "UpdatedTimestamp": "2025-07-22T21:17:34.792",
     "ReportingReceiptTypeId": null,
     "ShipmentAsnAssociation": [
         {
-            "ShipmentId": "900000119",
-            "UpdatedTimestamp": "2025-07-22T00:36:50.719",
+            "ShipmentId": "900000122",
+            "UpdatedTimestamp": "2025-07-22T21:17:29.262",
             "CreatedBy": "vgana3",
-            "CreatedTimestamp": "2025-07-22T00:36:50.719",
+            "CreatedTimestamp": "2025-07-22T21:17:29.262",
             "BusinessUnitId": null,
             "Process": "/shipmentAsnAssociation/bulkImport/",
             "OrgId": "1081",
             "FacilityId": "1081",
             "UpdatedBy": "vgana3",
-            "ContextId": "79337e49f1c176db::f388f0bf67aae0a0",
-            "PK": "7531446107198792907",
+            "ContextId": "bfb95985b70b6355::38f7b513831087e",
+            "PK": "7532190492626575296",
             "PurgeDate": null,
             "Asn": {
-                "AsnId": "VGASN2107QA9450"
+                "AsnId": "VGASN0722QA6520"
             },
-            "AsnId": "VGASN2107QA9450",
-            "Unique_Identifier": "7531446107198792907__VGASN2107QA9450"
+            "AsnId": "VGASN0722QA6520",
+            "Unique_Identifier": "7532190492626575296__VGASN0722QA6520"
         }
     ],
     "EstimatedDeliveryDate": null,
-    "ReceivedLpns": 2.0,
+    "ReceivedLpns": 0.0,
     "EntityLabels": null,
     "RrnId": null,
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7531445587338658994",
+    "PK": "7532189860896292641",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7531445587338658994__VGASN2107QA9450"
+    "Unique_Identifier": "7532189860896292641__VGASN0722QA6520"
 }</t>
         </is>
       </c>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -539,7 +539,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VGASN0722QA4571</t>
+          <t>VGASN0724QA6570</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0000VG07222025QA49200002</t>
+          <t>00V07242025QA8500</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -570,27 +570,19 @@
       <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BOLQA07222545</t>
+          <t>BOLQA07242537</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PROQA07222545</t>
+          <t>PROQA07242537</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -619,7 +611,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TRLQA07222545</t>
+          <t>TRLQA07242537</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -629,14 +621,14 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-07-22T21:17:34.423</t>
+          <t>2025-07-25T00:24:40.543</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VGASN0722QA4571</t>
+          <t>VGASN0724QA6570</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,7 +643,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0000VG07222025QA20210003</t>
+          <t>00V07242025QA4121</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -667,27 +659,19 @@
       <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BOLQA07222545</t>
+          <t>BOLQA07242537</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PROQA07222545</t>
+          <t>PROQA07242537</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -716,7 +700,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>TRLQA07222545</t>
+          <t>TRLQA07242537</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -726,14 +710,14 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-07-22T21:17:34.424</t>
+          <t>2025-07-25T00:24:40.544</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VGASN0722QA6520</t>
+          <t>VGASN0724QA8711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -748,7 +732,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0000VG07222025QA43750000</t>
+          <t>00V07242025QA4162</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -764,27 +748,19 @@
       <c r="G4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BOLQA07222579</t>
+          <t>BOLQA07242571</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PROQA07222579</t>
+          <t>PROQA07242571</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -813,7 +789,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>TRLQA07222579</t>
+          <t>TRLQA07242571</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -823,14 +799,14 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-07-22T21:17:34.412</t>
+          <t>2025-07-25T00:24:41.87</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VGASN0722QA6520</t>
+          <t>VGASN0724QA8711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -845,7 +821,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0000VG07222025QA14210001</t>
+          <t>00V07242025QA4223</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -861,27 +837,19 @@
       <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>BOLQA07222579</t>
+          <t>BOLQA07242571</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PROQA07222579</t>
+          <t>PROQA07242571</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -910,7 +878,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TRLQA07222579</t>
+          <t>TRLQA07242571</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -920,7 +888,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-07-22T21:17:34.422</t>
+          <t>2025-07-25T00:24:41.871</t>
         </is>
       </c>
     </row>
@@ -950,17 +918,17 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-07-22T21:16:26.09",
+    "CreatedTimestamp": "2025-07-25T00:24:41.868",
     "AsnRequestedService": [],
     "EstimatedWeight": 4.8,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
-        "ProNumber": "PROQA07222579",
+        "ProNumber": "PROQA07242571",
         "ShipmentStart": null,
         "ShipToCustomerName": null,
         "ExpediteFlag": false,
-        "SealNumber": "SLQA07222579",
+        "SealNumber": "SLQA07242571",
         "MinimumLPNStatus": null,
         "SoldToCustomerName": null,
         "Digital": null,
@@ -968,12 +936,12 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": "BOLQA07222579",
+        "BolNumber": "BOLQA07242571",
         "ShipmentCreateDate": null,
         "SalesOrderType": null
     },
-    "Process": "AsnStatusUpdate",
-    "ProNumber": "PROQA07222579",
+    "Process": "AsnHeaderMetricsService",
+    "ProNumber": "PROQA07242571",
     "DestinationFacilityAliasId": null,
     "UpdatedBy": "vgana3",
     "AsnLine": [],
@@ -985,8 +953,8 @@
     "BusinessUnitId": null,
     "PreDeterminedLpnCount": 2.0,
     "AsnVerificationDate": null,
-    "PreReceiptStatusId": "3",
-    "ContextId": "a659db5148b4dbd8::8c8ec38e191c5875",
+    "PreReceiptStatusId": null,
+    "ContextId": "63076fee68d4637f::e1a298798960b736",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
@@ -994,10 +962,10 @@
     "VendorId": null,
     "ShippedDate": null,
     "AsnStatus": "1000",
-    "BillOfLadingNumber": "BOLQA07222579",
+    "BillOfLadingNumber": "BOLQA07242571",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-07-22T21:16:26.189",
+            "CreatedTimestamp": "2025-07-25T00:24:41.869",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "EstimatedWeight": null,
@@ -1009,8 +977,8 @@
                 "DestinationFacilityId": null,
                 "LpnWidth": 12.0
             },
-            "DiversionCodeId": "STORAGE",
-            "Process": "PreReceiptResponseProcessingService",
+            "DiversionCodeId": null,
+            "Process": "/asn/save",
             "ItemAttributesValidated": true,
             "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
@@ -1019,15 +987,15 @@
             "LpnSizeTypeId": "CARTON",
             "FacilityTimezone": "Japan",
             "Asn": {
-                "AsnId": "VGASN0722QA6520"
+                "AsnId": "VGASN0724QA8711"
             },
-            "AsnId": "VGASN0722QA6520",
-            "UpdatedTimestamp": "2025-07-22T21:17:34.233",
+            "AsnId": "VGASN0724QA8711",
+            "UpdatedTimestamp": "2025-07-25T00:24:41.975",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "AllocationTypeId": "ProcessNeed",
-            "LpnId": "0000VG07222025QA43750000",
+            "AllocationTypeId": null,
+            "LpnId": "00V07242025QA4162",
             "BusinessUnitId": null,
             "LpnStatus": "1000",
             "LocationId": null,
@@ -1036,7 +1004,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-22T21:16:26.256",
+                    "CreatedTimestamp": "2025-07-25T00:24:41.87",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -1044,7 +1012,7 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "PreReceiptResponseProcessingService",
+                    "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
                     "ItemId": "DD9293-100-7",
@@ -1062,15 +1030,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
-                    "LpnDetailId": "f1acce19-744c-4ea2-809c-2381ae2067bd",
+                    "ContextId": "63076fee68d4637f::58d35a7760b02734",
+                    "LpnDetailId": "315f8346-9312-44b3-ad96-47f29c20e747",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7532189861886301493
+                        "PK": 7534030818698122856
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -1082,8 +1050,8 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-22T21:17:34.412",
-                    "PrereceiptAllocatedQuantity": 0.0,
+                    "UpdatedTimestamp": "2025-07-25T00:24:41.87",
+                    "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
                     "ShippedQuantity": 6.0,
@@ -1091,8 +1059,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7532189862556319133",
-                    "Unique_Identifier": "7532189862556319133__f1acce19-744c-4ea2-809c-2381ae2067bd"
+                    "PK": "7534030818708139139",
+                    "Unique_Identifier": "7534030818708139139__315f8346-9312-44b3-ad96-47f29c20e747"
                 }
             ],
             "EntityLabels": null,
@@ -1100,18 +1068,18 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": null,
-            "PreReceiptStatusId": "3",
+            "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
+            "ContextId": "63076fee68d4637f::58d35a7760b02734",
             "Canceled": false,
-            "PK": "7532189861886301493",
-            "Unique_Identifier": "7532189861886301493__0000VG07222025QA43750000",
+            "PK": "7534030818698122856",
+            "Unique_Identifier": "7534030818698122856__00V07242025QA4162",
             "DimensionUomId": null,
             "EstimationGroupId": null
         },
         {
-            "CreatedTimestamp": "2025-07-22T21:16:26.306",
+            "CreatedTimestamp": "2025-07-25T00:24:41.87",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "EstimatedWeight": null,
@@ -1123,8 +1091,8 @@
                 "DestinationFacilityId": null,
                 "LpnWidth": 12.0
             },
-            "DiversionCodeId": "STORAGE",
-            "Process": "PreReceiptResponseProcessingService",
+            "DiversionCodeId": null,
+            "Process": "/asn/save",
             "ItemAttributesValidated": true,
             "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
@@ -1133,15 +1101,15 @@
             "LpnSizeTypeId": "CARTON",
             "FacilityTimezone": "Japan",
             "Asn": {
-                "AsnId": "VGASN0722QA6520"
+                "AsnId": "VGASN0724QA8711"
             },
-            "AsnId": "VGASN0722QA6520",
-            "UpdatedTimestamp": "2025-07-22T21:17:34.258",
+            "AsnId": "VGASN0724QA8711",
+            "UpdatedTimestamp": "2025-07-25T00:24:41.981",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "AllocationTypeId": "ProcessNeed",
-            "LpnId": "0000VG07222025QA14210001",
+            "AllocationTypeId": null,
+            "LpnId": "00V07242025QA4223",
             "BusinessUnitId": null,
             "LpnStatus": "1000",
             "LocationId": null,
@@ -1150,7 +1118,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-22T21:16:26.308",
+                    "CreatedTimestamp": "2025-07-25T00:24:41.871",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -1158,7 +1126,7 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "PreReceiptResponseProcessingService",
+                    "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
                     "ItemId": "DD9293-100-7",
@@ -1176,15 +1144,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
-                    "LpnDetailId": "b658053a-818a-433a-a8a6-d05d07bb304d",
+                    "ContextId": "63076fee68d4637f::58d35a7760b02734",
+                    "LpnDetailId": "0c83595a-49dd-409e-89e8-3b645a94f19b",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7532189863066328041
+                        "PK": 7534030818708145638
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -1196,8 +1164,8 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-22T21:17:34.422",
-                    "PrereceiptAllocatedQuantity": 0.0,
+                    "UpdatedTimestamp": "2025-07-25T00:24:41.871",
+                    "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
                     "ShippedQuantity": 6.0,
@@ -1205,8 +1173,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7532189863086332237",
-                    "Unique_Identifier": "7532189863086332237__b658053a-818a-433a-a8a6-d05d07bb304d"
+                    "PK": "7534030818708153321",
+                    "Unique_Identifier": "7534030818708153321__0c83595a-49dd-409e-89e8-3b645a94f19b"
                 }
             ],
             "EntityLabels": null,
@@ -1214,18 +1182,18 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": null,
-            "PreReceiptStatusId": "3",
+            "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "a659db5148b4dbd8::500d5321bee910b7",
+            "ContextId": "63076fee68d4637f::58d35a7760b02734",
             "Canceled": false,
-            "PK": "7532189863066328041",
-            "Unique_Identifier": "7532189863066328041__0000VG07222025QA14210001",
+            "PK": "7534030818708145638",
+            "Unique_Identifier": "7534030818708145638__00V07242025QA4223",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA07222579",
+    "TrailerId": "TRLQA07242571",
     "FirstReceiptDate": null,
     "LastReceiptDate": null,
     "CarrierId": "AUPU",
@@ -1233,29 +1201,29 @@
     "EstimatedVolume": 56628.0,
     "OriginFacilityId": "0005005401",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0722QA6520",
+    "AsnId": "VGASN0724QA8711",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-07-22T21:17:34.792",
+    "UpdatedTimestamp": "2025-07-25T00:24:54.632",
     "ReportingReceiptTypeId": null,
     "ShipmentAsnAssociation": [
         {
-            "ShipmentId": "900000122",
-            "UpdatedTimestamp": "2025-07-22T21:17:29.262",
+            "ShipmentId": "900000156",
+            "UpdatedTimestamp": "2025-07-25T00:25:34.042",
             "CreatedBy": "vgana3",
-            "CreatedTimestamp": "2025-07-22T21:17:29.262",
+            "CreatedTimestamp": "2025-07-25T00:25:34.042",
             "BusinessUnitId": null,
             "Process": "/shipmentAsnAssociation/bulkImport/",
             "OrgId": "1081",
             "FacilityId": "1081",
             "UpdatedBy": "vgana3",
-            "ContextId": "bfb95985b70b6355::38f7b513831087e",
-            "PK": "7532190492626575296",
+            "ContextId": "6f44c1dcfae74e68::7b19d74d49fdd049",
+            "PK": "7534031340428282475",
             "PurgeDate": null,
             "Asn": {
-                "AsnId": "VGASN0722QA6520"
+                "AsnId": "VGASN0724QA8711"
             },
-            "AsnId": "VGASN0722QA6520",
-            "Unique_Identifier": "7532190492626575296__VGASN0722QA6520"
+            "AsnId": "VGASN0724QA8711",
+            "Unique_Identifier": "7534031340428282475__VGASN0724QA8711"
         }
     ],
     "EstimatedDeliveryDate": null,
@@ -1265,9 +1233,9 @@
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7532189860896292641",
+    "PK": "7534030818688116752",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7532189860896292641__VGASN0722QA6520"
+    "Unique_Identifier": "7534030818688116752__VGASN0724QA8711"
 }</t>
         </is>
       </c>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,12 +539,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VGASN0724QA6570</t>
+          <t>VGASN0729QA2870</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA8500</t>
+          <t>00V07292025QA3950</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -570,19 +570,27 @@
       <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BOLQA07242537</t>
+          <t>BOLQA07292530</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PROQA07242537</t>
+          <t>PROQA07292530</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -611,7 +619,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TRLQA07242537</t>
+          <t>TRLQA07292530</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -621,274 +629,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-07-25T00:24:40.543</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>VGASN0724QA6570</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V07242025QA4121</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>BOLQA07242537</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>PROQA07242537</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>CARTON</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>24</v>
-      </c>
-      <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>TRLQA07242537</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2025-07-25T00:24:40.544</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>VGASN0724QA8711</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V07242025QA4162</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>BOLQA07242571</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>PROQA07242571</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>CARTON</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>24</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>12</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>TRLQA07242571</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2025-07-25T00:24:41.87</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGASN0724QA8711</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V07242025QA4223</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>BOLQA07242571</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>PROQA07242571</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>CARTON</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>TRLQA07242571</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2025-07-25T00:24:41.871</t>
+          <t>2025-07-29T13:35:27.015</t>
         </is>
       </c>
     </row>
@@ -918,17 +659,17 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-07-25T00:24:41.868",
+    "CreatedTimestamp": "2025-07-29T13:35:03.483",
     "AsnRequestedService": [],
-    "EstimatedWeight": 4.8,
+    "EstimatedWeight": 2.4,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
-        "ProNumber": "PROQA07242571",
+        "ProNumber": "PROQA07292530",
         "ShipmentStart": null,
         "ShipToCustomerName": null,
         "ExpediteFlag": false,
-        "SealNumber": "SLQA07242571",
+        "SealNumber": "SLQA07292530",
         "MinimumLPNStatus": null,
         "SoldToCustomerName": null,
         "Digital": null,
@@ -936,75 +677,77 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": "BOLQA07242571",
+        "BolNumber": "BOLQA07292530",
         "ShipmentCreateDate": null,
         "SalesOrderType": null
     },
-    "Process": "AsnHeaderMetricsService",
-    "ProNumber": "PROQA07242571",
+    "Process": "AsnPurgeService",
+    "ProNumber": "PROQA07292530",
     "DestinationFacilityAliasId": null,
     "UpdatedBy": "vgana3",
     "AsnLine": [],
     "EstimatedReceiptDate": null,
-    "PurgeDate": null,
+    "PurgeDate": "2025-10-27T13:35:26.992",
     "ReferenceShipmentId": null,
     "CreatedBy": "vgana3",
-    "VerificationAttempted": false,
+    "VerificationAttempted": true,
     "BusinessUnitId": null,
-    "PreDeterminedLpnCount": 2.0,
-    "AsnVerificationDate": null,
-    "PreReceiptStatusId": null,
-    "ContextId": "63076fee68d4637f::e1a298798960b736",
+    "PreDeterminedLpnCount": 1.0,
+    "AsnVerificationDate": "2025-07-29T13:35:26.812",
+    "PreReceiptStatusId": "4",
+    "ContextId": "6aec3de0ac974f3a::e043e43f04377278",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
     "OriginFacilityAliasId": null,
     "VendorId": null,
     "ShippedDate": null,
-    "AsnStatus": "1000",
-    "BillOfLadingNumber": "BOLQA07242571",
+    "AsnStatus": "8000",
+    "BillOfLadingNumber": "BOLQA07292530",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-07-25T00:24:41.869",
+            "CreatedTimestamp": "2025-07-29T13:35:03.49",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
-            "EstimatedWeight": null,
             "FinalDestinationFacilityId": null,
             "VendorId": null,
+            "EstimatedWeight": null,
             "Extended": {
                 "LpnLength": 24.0,
                 "LpnHeight": 12.0,
                 "DestinationFacilityId": null,
                 "LpnWidth": 12.0
             },
-            "DiversionCodeId": null,
-            "Process": "/asn/save",
+            "DiversionCodeId": "STORAGE",
+            "Process": "AsnPurgeService",
             "ItemAttributesValidated": true,
             "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
-            "PurgeDate": null,
+            "Height": null,
             "FinalDestinationAddress": null,
+            "PurgeDate": "2025-10-27T13:35:26.992",
+            "Width": null,
             "LpnSizeTypeId": "CARTON",
+            "Asn": {
+                "AsnId": "VGASN0729QA2870"
+            },
             "FacilityTimezone": "Japan",
-            "Asn": {
-                "AsnId": "VGASN0724QA8711"
-            },
-            "AsnId": "VGASN0724QA8711",
-            "UpdatedTimestamp": "2025-07-25T00:24:41.975",
+            "AsnId": "VGASN0729QA2870",
+            "UpdatedTimestamp": "2025-07-29T13:35:27.015",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "AllocationTypeId": null,
-            "LpnId": "00V07242025QA4162",
+            "LpnId": "00V07292025QA3950",
+            "AllocationTypeId": "ProcessNeed",
             "BusinessUnitId": null,
-            "LpnStatus": "1000",
+            "LpnStatus": "4000",
             "LocationId": null,
             "LpnTypeId": "ILPN",
             "LpnDetail": [
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-25T00:24:41.87",
+                    "CreatedTimestamp": "2025-07-29T13:35:03.496",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -1012,7 +755,7 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
+                    "Process": "AsnPurgeService",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
                     "ItemId": "DD9293-100-7",
@@ -1021,7 +764,7 @@
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
                     "InventoryAttribute4": null,
-                    "PurgeDate": null,
+                    "PurgeDate": "2025-10-27T13:35:26.992",
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
                     "CreatedBy": "vgana3",
@@ -1030,15 +773,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "63076fee68d4637f::58d35a7760b02734",
-                    "LpnDetailId": "315f8346-9312-44b3-ad96-47f29c20e747",
+                    "ContextId": "6aec3de0ac974f3a::e043e43f04377278",
+                    "LpnDetailId": "d79a6108-f1ca-431d-883c-d2c2f51a1b8f",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7534030818698122856
+                        "PK": 7537961034908895843
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -1050,8 +793,8 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-25T00:24:41.87",
-                    "PrereceiptAllocatedQuantity": null,
+                    "UpdatedTimestamp": "2025-07-29T13:35:27.015",
+                    "PrereceiptAllocatedQuantity": 0.0,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
                     "ShippedQuantity": 6.0,
@@ -1059,8 +802,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7534030818708139139",
-                    "Unique_Identifier": "7534030818708139139__315f8346-9312-44b3-ad96-47f29c20e747"
+                    "PK": "7537961034958908387",
+                    "Unique_Identifier": "7537961034958908387__d79a6108-f1ca-431d-883c-d2c2f51a1b8f"
                 }
             ],
             "EntityLabels": null,
@@ -1068,174 +811,61 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": null,
-            "PreReceiptStatusId": null,
+            "Length": null,
+            "PreReceiptStatusId": "4",
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "63076fee68d4637f::58d35a7760b02734",
+            "ContextId": "6aec3de0ac974f3a::e043e43f04377278",
             "Canceled": false,
-            "PK": "7534030818698122856",
-            "Unique_Identifier": "7534030818698122856__00V07242025QA4162",
-            "DimensionUomId": null,
-            "EstimationGroupId": null
-        },
-        {
-            "CreatedTimestamp": "2025-07-25T00:24:41.87",
-            "VolumeUomId": null,
-            "PhysicalEntityCodeId": null,
-            "EstimatedWeight": null,
-            "FinalDestinationFacilityId": null,
-            "VendorId": null,
-            "Extended": {
-                "LpnLength": 24.0,
-                "LpnHeight": 12.0,
-                "DestinationFacilityId": null,
-                "LpnWidth": 12.0
-            },
-            "DiversionCodeId": null,
-            "Process": "/asn/save",
-            "ItemAttributesValidated": true,
-            "UpdatedBy": "vgana3",
-            "LpnRequestedService": [],
-            "PurgeDate": null,
-            "FinalDestinationAddress": null,
-            "LpnSizeTypeId": "CARTON",
-            "FacilityTimezone": "Japan",
-            "Asn": {
-                "AsnId": "VGASN0724QA8711"
-            },
-            "AsnId": "VGASN0724QA8711",
-            "UpdatedTimestamp": "2025-07-25T00:24:41.981",
-            "MarkFor": null,
-            "CreatedBy": "vgana3",
-            "ParentLpnId": null,
-            "AllocationTypeId": null,
-            "LpnId": "00V07242025QA4223",
-            "BusinessUnitId": null,
-            "LpnStatus": "1000",
-            "LocationId": null,
-            "LpnTypeId": "ILPN",
-            "LpnDetail": [
-                {
-                    "ExpiryDate": null,
-                    "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-25T00:24:41.871",
-                    "Extended": {
-                        "CutNumber": null,
-                        "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": null,
-                        "DeliveryNoteItemNumber": null
-                    },
-                    "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
-                    "AsnLineId": null,
-                    "InventoryTypeId": null,
-                    "ItemId": "DD9293-100-7",
-                    "UpdatedBy": "vgana3",
-                    "InventoryAttribute1": "01000",
-                    "InventoryAttribute2": null,
-                    "InventoryAttribute3": null,
-                    "InventoryAttribute4": null,
-                    "PurgeDate": null,
-                    "InventoryAttribute5": null,
-                    "PurchaseOrderLineId": "",
-                    "CreatedBy": "vgana3",
-                    "BatchNumber": null,
-                    "BusinessUnitId": null,
-                    "StandardPackQuantity": null,
-                    "ExternalOrderId": null,
-                    "PurchaseOrderId": "25050501",
-                    "ContextId": "63076fee68d4637f::58d35a7760b02734",
-                    "LpnDetailId": "0c83595a-49dd-409e-89e8-3b645a94f19b",
-                    "OriginalShippingFacilityId": null,
-                    "StandardSubPackQuantity": null,
-                    "VendorId": null,
-                    "ExternalOrderLineId": null,
-                    "LpnDetailStatus": "1000",
-                    "Lpn": {
-                        "PK": 7534030818708145638
-                    },
-                    "QuantityUomId": "LPN",
-                    "SeasonYear": null,
-                    "ManufacturingDate": null,
-                    "Style": null,
-                    "ProductClass": null,
-                    "Season": null,
-                    "CrossReferenceOrderId": null,
-                    "HandlingUomQuantity": null,
-                    "TierQuantity": null,
-                    "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-25T00:24:41.871",
-                    "PrereceiptAllocatedQuantity": null,
-                    "LpnDetailAttribute": [],
-                    "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 6.0,
-                    "EntityLabels": null,
-                    "ProductStatusId": null,
-                    "OrgId": "1081",
-                    "FacilityId": "1081",
-                    "PK": "7534030818708153321",
-                    "Unique_Identifier": "7534030818708153321__0c83595a-49dd-409e-89e8-3b645a94f19b"
-                }
-            ],
-            "EntityLabels": null,
-            "WeightUomId": null,
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "Volume": null,
-            "PreReceiptStatusId": null,
-            "SingleItemLpn": true,
-            "PurchaseOrderId": "25050501",
-            "ContextId": "63076fee68d4637f::58d35a7760b02734",
-            "Canceled": false,
-            "PK": "7534030818708145638",
-            "Unique_Identifier": "7534030818708145638__00V07242025QA4223",
+            "PK": "7537961034908895843",
+            "Unique_Identifier": "7537961034908895843__00V07292025QA3950",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA07242571",
-    "FirstReceiptDate": null,
-    "LastReceiptDate": null,
+    "TrailerId": "TRLQA07292530",
+    "FirstReceiptDate": "2025-07-29T13:35:14.816",
+    "LastReceiptDate": "2025-07-29T13:35:14.816",
     "CarrierId": "AUPU",
-    "ShippedLpns": 2.0,
-    "EstimatedVolume": 56628.0,
+    "ShippedLpns": 1.0,
+    "EstimatedVolume": 28314.0,
     "OriginFacilityId": "0005005401",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0724QA8711",
+    "AsnId": "VGASN0729QA2870",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-07-25T00:24:54.632",
+    "UpdatedTimestamp": "2025-07-29T13:35:26.998",
     "ReportingReceiptTypeId": null,
     "ShipmentAsnAssociation": [
         {
-            "ShipmentId": "900000156",
-            "UpdatedTimestamp": "2025-07-25T00:25:34.042",
+            "ShipmentId": "900000227",
+            "UpdatedTimestamp": "2025-07-29T13:35:07.667",
             "CreatedBy": "vgana3",
-            "CreatedTimestamp": "2025-07-25T00:25:34.042",
+            "CreatedTimestamp": "2025-07-29T13:35:07.667",
             "BusinessUnitId": null,
             "Process": "/shipmentAsnAssociation/bulkImport/",
             "OrgId": "1081",
             "FacilityId": "1081",
             "UpdatedBy": "vgana3",
-            "ContextId": "6f44c1dcfae74e68::7b19d74d49fdd049",
-            "PK": "7534031340428282475",
+            "ContextId": "020453448bb8d360::34d1a765781e7e8",
+            "PK": "7537961076668985905",
             "PurgeDate": null,
             "Asn": {
-                "AsnId": "VGASN0724QA8711"
+                "AsnId": "VGASN0729QA2870"
             },
-            "AsnId": "VGASN0724QA8711",
-            "Unique_Identifier": "7534031340428282475__VGASN0724QA8711"
+            "AsnId": "VGASN0729QA2870",
+            "Unique_Identifier": "7537961076668985905__VGASN0729QA2870"
         }
     ],
     "EstimatedDeliveryDate": null,
-    "ReceivedLpns": 0.0,
+    "ReceivedLpns": 1.0,
     "EntityLabels": null,
     "RrnId": null,
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7534030818688116752",
+    "PK": "7537961034818882919",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7534030818688116752__VGASN0724QA8711"
+    "Unique_Identifier": "7537961034818882919__VGASN0729QA2870"
 }</t>
         </is>
       </c>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -539,12 +539,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2870</t>
+          <t>VGASN0807QA1250</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,43 +554,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3950</t>
+          <t>00V08072025QA4330</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BOLQA07292530</t>
+          <t>BOLQA08072586</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PROQA07292530</t>
+          <t>PROQA08072586</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -619,7 +611,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TRLQA07292530</t>
+          <t>TRLQA08072586</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -629,7 +621,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-07-29T13:35:27.015</t>
+          <t>2025-08-07T13:42:46.259</t>
         </is>
       </c>
     </row>
@@ -659,17 +651,17 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-07-29T13:35:03.483",
+    "CreatedTimestamp": "2025-08-07T13:13:44.164",
     "AsnRequestedService": [],
-    "EstimatedWeight": 2.4,
+    "EstimatedWeight": 4.8,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
-        "ProNumber": "PROQA07292530",
+        "ProNumber": null,
         "ShipmentStart": null,
         "ShipToCustomerName": null,
-        "ExpediteFlag": false,
-        "SealNumber": "SLQA07292530",
+        "ExpediteFlag": true,
+        "SealNumber": null,
         "MinimumLPNStatus": null,
         "SoldToCustomerName": null,
         "Digital": null,
@@ -677,36 +669,37 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": "BOLQA07292530",
+        "BolNumber": null,
         "ShipmentCreateDate": null,
         "SalesOrderType": null
     },
-    "Process": "AsnPurgeService",
-    "ProNumber": "PROQA07292530",
+    "Process": "AsnHeaderMetricsService",
+    "ProNumber": "PROQA08072586",
     "DestinationFacilityAliasId": null,
     "UpdatedBy": "vgana3",
     "AsnLine": [],
     "EstimatedReceiptDate": null,
-    "PurgeDate": "2025-10-27T13:35:26.992",
+    "PurgeDate": null,
     "ReferenceShipmentId": null,
     "CreatedBy": "vgana3",
-    "VerificationAttempted": true,
+    "VerificationAttempted": false,
     "BusinessUnitId": null,
     "PreDeterminedLpnCount": 1.0,
-    "AsnVerificationDate": "2025-07-29T13:35:26.812",
-    "PreReceiptStatusId": "4",
-    "ContextId": "6aec3de0ac974f3a::e043e43f04377278",
+    "AsnVerificationDate": null,
+    "PreReceiptStatusId": null,
+    "ContextId": "3bca5c5698039350::876842653e74ba85",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
     "OriginFacilityAliasId": null,
     "VendorId": null,
     "ShippedDate": null,
-    "AsnStatus": "8000",
-    "BillOfLadingNumber": "BOLQA07292530",
+    "AlternateAsnId": null,
+    "AsnStatus": "1000",
+    "BillOfLadingNumber": "BOLQA08072586",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-07-29T13:35:03.49",
+            "CreatedTimestamp": "2025-08-07T13:42:46.257",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
@@ -718,36 +711,36 @@
                 "DestinationFacilityId": null,
                 "LpnWidth": 12.0
             },
-            "DiversionCodeId": "STORAGE",
-            "Process": "AsnPurgeService",
+            "DiversionCodeId": null,
+            "Process": "/asn/save",
             "ItemAttributesValidated": true,
             "UpdatedBy": "vgana3",
             "LpnRequestedService": [],
             "Height": null,
             "FinalDestinationAddress": null,
-            "PurgeDate": "2025-10-27T13:35:26.992",
+            "PurgeDate": null,
             "Width": null,
             "LpnSizeTypeId": "CARTON",
             "Asn": {
-                "AsnId": "VGASN0729QA2870"
+                "AsnId": "VGASN0807QA1250"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0729QA2870",
-            "UpdatedTimestamp": "2025-07-29T13:35:27.015",
+            "AsnId": "VGASN0807QA1250",
+            "UpdatedTimestamp": "2025-08-07T13:42:46.384",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "LpnId": "00V07292025QA3950",
-            "AllocationTypeId": "ProcessNeed",
+            "LpnId": "00V08072025QA4330",
+            "AllocationTypeId": null,
             "BusinessUnitId": null,
-            "LpnStatus": "4000",
+            "LpnStatus": "1000",
             "LocationId": null,
             "LpnTypeId": "ILPN",
             "LpnDetail": [
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-07-29T13:35:03.496",
+                    "CreatedTimestamp": "2025-08-07T13:42:46.259",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -755,16 +748,16 @@
                         "DeliveryNoteItemNumber": null
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "AsnPurgeService",
+                    "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "DD9293-100-7",
+                    "ItemId": "924156-100-S",
                     "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
                     "InventoryAttribute4": null,
-                    "PurgeDate": "2025-10-27T13:35:26.992",
+                    "PurgeDate": null,
                     "InventoryAttribute5": null,
                     "PurchaseOrderLineId": "",
                     "CreatedBy": "vgana3",
@@ -773,15 +766,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "6aec3de0ac974f3a::e043e43f04377278",
-                    "LpnDetailId": "d79a6108-f1ca-431d-883c-d2c2f51a1b8f",
+                    "ContextId": "10ec9d87d2a09ac3::abc9ec6cff6a4692",
+                    "LpnDetailId": "89ecc640-3245-40d2-9df9-9e3ff5b34304",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7537961034908895843
+                        "PK": 7545741662566628014
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -793,8 +786,8 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-07-29T13:35:27.015",
-                    "PrereceiptAllocatedQuantity": 0.0,
+                    "UpdatedTimestamp": "2025-08-07T13:42:46.259",
+                    "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
                     "ShippedQuantity": 6.0,
@@ -802,8 +795,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7537961034958908387",
-                    "Unique_Identifier": "7537961034958908387__d79a6108-f1ca-431d-883c-d2c2f51a1b8f"
+                    "PK": "7545741662596638476",
+                    "Unique_Identifier": "7545741662596638476__89ecc640-3245-40d2-9df9-9e3ff5b34304"
                 }
             ],
             "EntityLabels": null,
@@ -812,60 +805,40 @@
             "FacilityId": "1081",
             "Volume": null,
             "Length": null,
-            "PreReceiptStatusId": "4",
+            "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "6aec3de0ac974f3a::e043e43f04377278",
+            "ContextId": "10ec9d87d2a09ac3::abc9ec6cff6a4692",
             "Canceled": false,
-            "PK": "7537961034908895843",
-            "Unique_Identifier": "7537961034908895843__00V07292025QA3950",
+            "PK": "7545741662566628014",
+            "Unique_Identifier": "7545741662566628014__00V08072025QA4330",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA07292530",
-    "FirstReceiptDate": "2025-07-29T13:35:14.816",
-    "LastReceiptDate": "2025-07-29T13:35:14.816",
+    "TrailerId": "TRLQA08072586",
+    "FirstReceiptDate": null,
+    "LastReceiptDate": null,
     "CarrierId": "AUPU",
     "ShippedLpns": 1.0,
-    "EstimatedVolume": 28314.0,
+    "EstimatedVolume": 34560.0,
     "OriginFacilityId": "0005005401",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0729QA2870",
+    "AsnId": "VGASN0807QA1250",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-07-29T13:35:26.998",
+    "UpdatedTimestamp": "2025-08-07T13:43:22.592",
     "ReportingReceiptTypeId": null,
-    "ShipmentAsnAssociation": [
-        {
-            "ShipmentId": "900000227",
-            "UpdatedTimestamp": "2025-07-29T13:35:07.667",
-            "CreatedBy": "vgana3",
-            "CreatedTimestamp": "2025-07-29T13:35:07.667",
-            "BusinessUnitId": null,
-            "Process": "/shipmentAsnAssociation/bulkImport/",
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "UpdatedBy": "vgana3",
-            "ContextId": "020453448bb8d360::34d1a765781e7e8",
-            "PK": "7537961076668985905",
-            "PurgeDate": null,
-            "Asn": {
-                "AsnId": "VGASN0729QA2870"
-            },
-            "AsnId": "VGASN0729QA2870",
-            "Unique_Identifier": "7537961076668985905__VGASN0729QA2870"
-        }
-    ],
+    "ShipmentAsnAssociation": [],
     "EstimatedDeliveryDate": null,
-    "ReceivedLpns": 1.0,
+    "ReceivedLpns": 0.0,
     "EntityLabels": null,
     "RrnId": null,
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7537961034818882919",
+    "PK": "7545724241635401291",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7537961034818882919__VGASN0729QA2870"
+    "Unique_Identifier": "7545724241635401291__VGASN0807QA1250"
 }</t>
         </is>
       </c>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D9A0C9-0F03-BC46-8808-1F5294C44D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36042E74-BD37-B448-AD50-F87B6CF8F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="36000" windowHeight="23380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASN_Details" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>AsnId</t>
   </si>
@@ -32,6 +32,9 @@
     <t>AsnOriginTypeId</t>
   </si>
   <si>
+    <t>InboundDelivery</t>
+  </si>
+  <si>
     <t>LpnId</t>
   </si>
   <si>
@@ -86,25 +89,28 @@
     <t>UpdatedTimestamp</t>
   </si>
   <si>
-    <t>VGASN0820QA1882</t>
+    <t>VGASN0824QA1080</t>
   </si>
   <si>
     <t>1000</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>00V08072025QA3981254603</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>BOLQA08202572</t>
-  </si>
-  <si>
-    <t>PROQA08202572</t>
+    <t>P</t>
+  </si>
+  <si>
+    <t>900000409</t>
+  </si>
+  <si>
+    <t>00V08242025QA60500</t>
+  </si>
+  <si>
+    <t>924156-365-M</t>
+  </si>
+  <si>
+    <t>BOLQA08242582</t>
+  </si>
+  <si>
+    <t>PROQA08242582</t>
   </si>
   <si>
     <t>AUPU</t>
@@ -116,25 +122,31 @@
     <t>0005005401</t>
   </si>
   <si>
-    <t>TRLQA08202572</t>
+    <t>TRLQA08242582</t>
   </si>
   <si>
     <t>vgana3</t>
   </si>
   <si>
-    <t>2025-08-20T16:17:35.752</t>
-  </si>
-  <si>
-    <t>VGASN0820QA1883</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>00V08072025QA3981254604</t>
-  </si>
-  <si>
-    <t>2025-08-20T16:19:01.313</t>
+    <t>2025-08-24T18:30:58.593</t>
+  </si>
+  <si>
+    <t>00V08242025QA58401</t>
+  </si>
+  <si>
+    <t>924157-417-2XL</t>
+  </si>
+  <si>
+    <t>2025-08-24T18:30:58.643</t>
+  </si>
+  <si>
+    <t>00V08242025QA76102</t>
+  </si>
+  <si>
+    <t>924156-836-XL</t>
+  </si>
+  <si>
+    <t>2025-08-24T18:30:58.645</t>
   </si>
   <si>
     <t>Raw_Payload</t>
@@ -142,9 +154,9 @@
   <si>
     <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-08-20T16:19:01.31",
+    "CreatedTimestamp": "2025-08-24T18:30:58.369",
     "AsnRequestedService": [],
-    "EstimatedWeight": 4.8,
+    "EstimatedWeight": 0.0,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
@@ -165,7 +177,7 @@
         "SalesOrderType": null
     },
     "Process": "AsnHeaderMetricsService",
-    "ProNumber": "PROQA08202572",
+    "ProNumber": "PROQA08242582",
     "DestinationFacilityAliasId": null,
     "UpdatedBy": "vgana3",
     "AsnLine": [],
@@ -175,10 +187,10 @@
     "CreatedBy": "vgana3",
     "VerificationAttempted": false,
     "BusinessUnitId": null,
-    "PreDeterminedLpnCount": 1.0,
+    "PreDeterminedLpnCount": 3.0,
     "AsnVerificationDate": null,
     "PreReceiptStatusId": null,
-    "ContextId": "ed1db505c69e25b1::2da959ecb8d5f959",
+    "ContextId": "510b4a8038998b77::65acb7da9494b5cd",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
@@ -187,10 +199,10 @@
     "ShippedDate": null,
     "AlternateAsnId": null,
     "AsnStatus": "1000",
-    "BillOfLadingNumber": "BOLQA08202572",
+    "BillOfLadingNumber": "BOLQA08242582",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-08-20T16:19:01.312",
+            "CreatedTimestamp": "2025-08-24T18:30:58.533",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
@@ -213,15 +225,15 @@
             "Width": null,
             "LpnSizeTypeId": "CARTON",
             "Asn": {
-                "AsnId": "VGASN0820QA1883"
+                "AsnId": "VGASN0824QA1080"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0820QA1883",
-            "UpdatedTimestamp": "2025-08-20T16:19:01.511",
+            "AsnId": "VGASN0824QA1080",
+            "UpdatedTimestamp": "2025-08-24T18:31:02.204",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "LpnId": "00V08072025QA3981254604",
+            "LpnId": "00V08242025QA60500",
             "AllocationTypeId": null,
             "BusinessUnitId": null,
             "LpnStatus": "1000",
@@ -231,7 +243,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-08-20T16:19:01.313",
+                    "CreatedTimestamp": "2025-08-24T18:30:58.593",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -242,7 +254,7 @@
                     "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "924156-100-S",
+                    "ItemId": "924156-365-M",
                     "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
@@ -257,15 +269,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "ed1db505c69e25b1::64209c21d4f8417b",
-                    "LpnDetailId": "290b197b-f9b4-4a36-aee7-e7851298915b",
+                    "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+                    "LpnDetailId": "0bef30f5-5dbc-4061-9f01-296702556518",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7557067413118275969
+                        "PK": 7560602585333881188
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -277,7 +289,7 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-08-20T16:19:01.313",
+                    "UpdatedTimestamp": "2025-08-24T18:30:58.593",
                     "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
@@ -286,8 +298,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7557067413138288586",
-                    "Unique_Identifier": "7557067413138288586__290b197b-f9b4-4a36-aee7-e7851298915b"
+                    "PK": "7560602585923898271",
+                    "Unique_Identifier": "7560602585923898271__0bef30f5-5dbc-4061-9f01-296702556518"
                 }
             ],
             "EntityLabels": null,
@@ -299,27 +311,281 @@
             "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "ed1db505c69e25b1::64209c21d4f8417b",
+            "ContextId": "510b4a8038998b77::23ca8818abf02da5",
             "Canceled": false,
-            "PK": "7557067413118275969",
-            "Unique_Identifier": "7557067413118275969__00V08072025QA3981254604",
+            "PK": "7560602585333881188",
+            "Unique_Identifier": "7560602585333881188__00V08242025QA60500",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-08-24T18:30:58.641",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "EstimatedWeight": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": null,
+            "Process": "/asn/save",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "Height": null,
+            "FinalDestinationAddress": null,
+            "PurgeDate": null,
+            "Width": null,
+            "LpnSizeTypeId": "CARTON",
+            "Asn": {
+                "AsnId": "VGASN0824QA1080"
+            },
+            "FacilityTimezone": "Japan",
+            "AsnId": "VGASN0824QA1080",
+            "UpdatedTimestamp": "2025-08-24T18:31:02.205",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "LpnId": "00V08242025QA58401",
+            "AllocationTypeId": null,
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
+                {
+                    "ExpiryDate": null,
+                    "RetailPrice": null,
+                    "CreatedTimestamp": "2025-08-24T18:30:58.643",
+                    "Extended": {
+                        "CutNumber": null,
+                        "PurchaseOrderItemId": null,
+                        "UnitOfMeasureCode": null,
+                        "DeliveryNoteItemNumber": null
+                    },
+                    "CountryOfOrigin": "CN",
+                    "Process": "/asn/save",
+                    "AsnLineId": null,
+                    "InventoryTypeId": null,
+                    "ItemId": "924157-417-2XL",
+                    "UpdatedBy": "vgana3",
+                    "InventoryAttribute1": "01000",
+                    "InventoryAttribute2": null,
+                    "InventoryAttribute3": null,
+                    "InventoryAttribute4": null,
+                    "PurgeDate": null,
+                    "InventoryAttribute5": null,
+                    "PurchaseOrderLineId": "",
+                    "CreatedBy": "vgana3",
+                    "BatchNumber": null,
+                    "BusinessUnitId": null,
+                    "StandardPackQuantity": null,
+                    "ExternalOrderId": null,
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+                    "LpnDetailId": "4f571bcc-9f95-40f9-a38a-a2cd2a81f166",
+                    "OriginalShippingFacilityId": null,
+                    "StandardSubPackQuantity": null,
+                    "VendorId": null,
+                    "ExternalOrderLineId": null,
+                    "LpnDetailStatus": "1000",
+                    "Lpn": {
+                        "PK": 7560602586413902897
+                    },
+                    "QuantityUomId": "LPN",
+                    "SeasonYear": null,
+                    "ManufacturingDate": null,
+                    "Style": null,
+                    "ProductClass": null,
+                    "Season": null,
+                    "CrossReferenceOrderId": null,
+                    "HandlingUomQuantity": null,
+                    "TierQuantity": null,
+                    "CrossReferenceOrderLineId": null,
+                    "UpdatedTimestamp": "2025-08-24T18:30:58.643",
+                    "PrereceiptAllocatedQuantity": null,
+                    "LpnDetailAttribute": [],
+                    "LpnDetailGroupingId": null,
+                    "ShippedQuantity": 6.0,
+                    "EntityLabels": null,
+                    "ProductStatusId": null,
+                    "OrgId": "1081",
+                    "FacilityId": "1081",
+                    "PK": "7560602586423913842",
+                    "Unique_Identifier": "7560602586423913842__4f571bcc-9f95-40f9-a38a-a2cd2a81f166"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "Length": null,
+            "PreReceiptStatusId": null,
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+            "Canceled": false,
+            "PK": "7560602586413902897",
+            "Unique_Identifier": "7560602586413902897__00V08242025QA58401",
+            "DimensionUomId": null,
+            "EstimationGroupId": null
+        },
+        {
+            "CreatedTimestamp": "2025-08-24T18:30:58.644",
+            "VolumeUomId": null,
+            "PhysicalEntityCodeId": null,
+            "FinalDestinationFacilityId": null,
+            "VendorId": null,
+            "EstimatedWeight": null,
+            "Extended": {
+                "LpnLength": 24.0,
+                "LpnHeight": 12.0,
+                "DestinationFacilityId": null,
+                "LpnWidth": 12.0
+            },
+            "DiversionCodeId": null,
+            "Process": "/asn/save",
+            "ItemAttributesValidated": true,
+            "UpdatedBy": "vgana3",
+            "LpnRequestedService": [],
+            "Height": null,
+            "FinalDestinationAddress": null,
+            "PurgeDate": null,
+            "Width": null,
+            "LpnSizeTypeId": "CARTON",
+            "Asn": {
+                "AsnId": "VGASN0824QA1080"
+            },
+            "FacilityTimezone": "Japan",
+            "AsnId": "VGASN0824QA1080",
+            "UpdatedTimestamp": "2025-08-24T18:31:02.205",
+            "MarkFor": null,
+            "CreatedBy": "vgana3",
+            "ParentLpnId": null,
+            "LpnId": "00V08242025QA76102",
+            "AllocationTypeId": null,
+            "BusinessUnitId": null,
+            "LpnStatus": "1000",
+            "LocationId": null,
+            "LpnTypeId": "ILPN",
+            "LpnDetail": [
+                {
+                    "ExpiryDate": null,
+                    "RetailPrice": null,
+                    "CreatedTimestamp": "2025-08-24T18:30:58.645",
+                    "Extended": {
+                        "CutNumber": null,
+                        "PurchaseOrderItemId": null,
+                        "UnitOfMeasureCode": null,
+                        "DeliveryNoteItemNumber": null
+                    },
+                    "CountryOfOrigin": "CN",
+                    "Process": "/asn/save",
+                    "AsnLineId": null,
+                    "InventoryTypeId": null,
+                    "ItemId": "924156-836-XL",
+                    "UpdatedBy": "vgana3",
+                    "InventoryAttribute1": "01000",
+                    "InventoryAttribute2": null,
+                    "InventoryAttribute3": null,
+                    "InventoryAttribute4": null,
+                    "PurgeDate": null,
+                    "InventoryAttribute5": null,
+                    "PurchaseOrderLineId": "",
+                    "CreatedBy": "vgana3",
+                    "BatchNumber": null,
+                    "BusinessUnitId": null,
+                    "StandardPackQuantity": null,
+                    "ExternalOrderId": null,
+                    "PurchaseOrderId": "25050501",
+                    "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+                    "LpnDetailId": "426cec57-8e3f-46f0-9c5f-4966e80719a1",
+                    "OriginalShippingFacilityId": null,
+                    "StandardSubPackQuantity": null,
+                    "VendorId": null,
+                    "ExternalOrderLineId": null,
+                    "LpnDetailStatus": "1000",
+                    "Lpn": {
+                        "PK": 7560602586443921886
+                    },
+                    "QuantityUomId": "LPN",
+                    "SeasonYear": null,
+                    "ManufacturingDate": null,
+                    "Style": null,
+                    "ProductClass": null,
+                    "Season": null,
+                    "CrossReferenceOrderId": null,
+                    "HandlingUomQuantity": null,
+                    "TierQuantity": null,
+                    "CrossReferenceOrderLineId": null,
+                    "UpdatedTimestamp": "2025-08-24T18:30:58.645",
+                    "PrereceiptAllocatedQuantity": null,
+                    "LpnDetailAttribute": [],
+                    "LpnDetailGroupingId": null,
+                    "ShippedQuantity": 6.0,
+                    "EntityLabels": null,
+                    "ProductStatusId": null,
+                    "OrgId": "1081",
+                    "FacilityId": "1081",
+                    "PK": "7560602586453931673",
+                    "Unique_Identifier": "7560602586453931673__426cec57-8e3f-46f0-9c5f-4966e80719a1"
+                }
+            ],
+            "EntityLabels": null,
+            "WeightUomId": null,
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "Volume": null,
+            "Length": null,
+            "PreReceiptStatusId": null,
+            "SingleItemLpn": true,
+            "PurchaseOrderId": "25050501",
+            "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+            "Canceled": false,
+            "PK": "7560602586443921886",
+            "Unique_Identifier": "7560602586443921886__00V08242025QA76102",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA08202572",
+    "TrailerId": "TRLQA08242582",
     "FirstReceiptDate": null,
     "LastReceiptDate": null,
     "CarrierId": "AUPU",
-    "ShippedLpns": 1.0,
-    "EstimatedVolume": 34560.0,
+    "ShippedLpns": 3.0,
+    "EstimatedVolume": 0.0,
     "OriginFacilityId": "0005005401",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0820QA1883",
+    "AsnId": "VGASN0824QA1080",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-08-20T16:19:17.493",
+    "UpdatedTimestamp": "2025-08-24T18:31:13.869",
     "ReportingReceiptTypeId": null,
-    "ShipmentAsnAssociation": [],
+    "ShipmentAsnAssociation": [
+        {
+            "ShipmentId": "900000409",
+            "UpdatedTimestamp": "2025-08-24T18:31:12.794",
+            "CreatedBy": "vgana3",
+            "CreatedTimestamp": "2025-08-24T18:31:12.794",
+            "BusinessUnitId": null,
+            "Process": "/shipmentAsnAssociation/bulkImport/",
+            "OrgId": "1081",
+            "FacilityId": "1081",
+            "UpdatedBy": "vgana3",
+            "ContextId": "821c44ea024119b7::108c773b2bfecf82",
+            "PK": "7560602727944036481",
+            "PurgeDate": null,
+            "Asn": {
+                "AsnId": "VGASN0824QA1080"
+            },
+            "AsnId": "VGASN0824QA1080",
+            "Unique_Identifier": "7560602727944036481__VGASN0824QA1080"
+        }
+    ],
     "EstimatedDeliveryDate": null,
     "ReceivedLpns": 0.0,
     "EntityLabels": null,
@@ -327,9 +593,9 @@
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7557067413108265562",
+    "PK": "7560602583683873184",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7557067413108265562__VGASN0820QA1883"
+    "Unique_Identifier": "7560602583683873184__VGASN0824QA1080"
 }</t>
   </si>
 </sst>
@@ -694,33 +960,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,123 +1031,194 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2">
         <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2">
-        <v>24</v>
-      </c>
-      <c r="P2">
-        <v>12</v>
       </c>
       <c r="Q2">
         <v>12</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2">
+        <v>12</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
         <v>30</v>
       </c>
-      <c r="S2" t="s">
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="T2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3">
+      <c r="P3">
         <v>24</v>
-      </c>
-      <c r="P3">
-        <v>12</v>
       </c>
       <c r="Q3">
         <v>12</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3">
+        <v>12</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s">
         <v>30</v>
       </c>
-      <c r="S3" t="s">
+      <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="T3" t="s">
+      <c r="P4">
+        <v>24</v>
+      </c>
+      <c r="Q4">
+        <v>12</v>
+      </c>
+      <c r="R4">
+        <v>12</v>
+      </c>
+      <c r="S4" t="s">
         <v>32</v>
       </c>
-      <c r="U3" t="s">
-        <v>37</v>
+      <c r="T4" t="s">
+        <v>33</v>
+      </c>
+      <c r="U4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -915,12 +1233,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36042E74-BD37-B448-AD50-F87B6CF8F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89C2383-920B-9641-BB76-50BC7D975801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="34140" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASN_Details" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
   <si>
     <t>AsnId</t>
   </si>
@@ -32,7 +32,7 @@
     <t>AsnOriginTypeId</t>
   </si>
   <si>
-    <t>InboundDelivery</t>
+    <t>Expedited_Flag</t>
   </si>
   <si>
     <t>LpnId</t>
@@ -89,7 +89,7 @@
     <t>UpdatedTimestamp</t>
   </si>
   <si>
-    <t>VGASN0824QA1080</t>
+    <t>VGASN0829QA1160</t>
   </si>
   <si>
     <t>1000</t>
@@ -98,19 +98,16 @@
     <t>P</t>
   </si>
   <si>
-    <t>900000409</t>
-  </si>
-  <si>
-    <t>00V08242025QA60500</t>
-  </si>
-  <si>
-    <t>924156-365-M</t>
-  </si>
-  <si>
-    <t>BOLQA08242582</t>
-  </si>
-  <si>
-    <t>PROQA08242582</t>
+    <t>00V08292025QA72000</t>
+  </si>
+  <si>
+    <t>924157-447-XL</t>
+  </si>
+  <si>
+    <t>BOLQA08292555</t>
+  </si>
+  <si>
+    <t>PROQA08292555</t>
   </si>
   <si>
     <t>AUPU</t>
@@ -122,31 +119,58 @@
     <t>0005005401</t>
   </si>
   <si>
-    <t>TRLQA08242582</t>
+    <t>TRLQA08292555</t>
   </si>
   <si>
     <t>vgana3</t>
   </si>
   <si>
-    <t>2025-08-24T18:30:58.593</t>
-  </si>
-  <si>
-    <t>00V08242025QA58401</t>
-  </si>
-  <si>
-    <t>924157-417-2XL</t>
-  </si>
-  <si>
-    <t>2025-08-24T18:30:58.643</t>
-  </si>
-  <si>
-    <t>00V08242025QA76102</t>
-  </si>
-  <si>
-    <t>924156-836-XL</t>
-  </si>
-  <si>
-    <t>2025-08-24T18:30:58.645</t>
+    <t>2025-08-29T14:54:56.752</t>
+  </si>
+  <si>
+    <t>00V08292025QA36601</t>
+  </si>
+  <si>
+    <t>2025-08-29T14:54:56.755</t>
+  </si>
+  <si>
+    <t>00V08292025QA41302</t>
+  </si>
+  <si>
+    <t>2025-08-29T14:54:56.756</t>
+  </si>
+  <si>
+    <t>VGASN0829QA5450</t>
+  </si>
+  <si>
+    <t>00V08292025QA29403</t>
+  </si>
+  <si>
+    <t>DD9293-100-9.5</t>
+  </si>
+  <si>
+    <t>BOLQA08292599</t>
+  </si>
+  <si>
+    <t>PROQA08292599</t>
+  </si>
+  <si>
+    <t>TRLQA08292599</t>
+  </si>
+  <si>
+    <t>2025-08-29T14:54:59.435</t>
+  </si>
+  <si>
+    <t>00V08292025QA56604</t>
+  </si>
+  <si>
+    <t>2025-08-29T14:54:59.437</t>
+  </si>
+  <si>
+    <t>00V08292025QA88205</t>
+  </si>
+  <si>
+    <t>2025-08-29T14:54:59.438</t>
   </si>
   <si>
     <t>Raw_Payload</t>
@@ -154,9 +178,9 @@
   <si>
     <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-08-24T18:30:58.369",
+    "CreatedTimestamp": "2025-08-29T14:54:59.433",
     "AsnRequestedService": [],
-    "EstimatedWeight": 0.0,
+    "EstimatedWeight": 13.788,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
@@ -177,7 +201,7 @@
         "SalesOrderType": null
     },
     "Process": "AsnHeaderMetricsService",
-    "ProNumber": "PROQA08242582",
+    "ProNumber": "PROQA08292599",
     "DestinationFacilityAliasId": null,
     "UpdatedBy": "vgana3",
     "AsnLine": [],
@@ -190,7 +214,7 @@
     "PreDeterminedLpnCount": 3.0,
     "AsnVerificationDate": null,
     "PreReceiptStatusId": null,
-    "ContextId": "510b4a8038998b77::65acb7da9494b5cd",
+    "ContextId": "a567e18b7ac93933::f86cbe77148b9a54",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
@@ -199,10 +223,10 @@
     "ShippedDate": null,
     "AlternateAsnId": null,
     "AsnStatus": "1000",
-    "BillOfLadingNumber": "BOLQA08242582",
+    "BillOfLadingNumber": "BOLQA08292599",
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-08-24T18:30:58.533",
+            "CreatedTimestamp": "2025-08-29T14:54:59.434",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
@@ -225,15 +249,15 @@
             "Width": null,
             "LpnSizeTypeId": "CARTON",
             "Asn": {
-                "AsnId": "VGASN0824QA1080"
+                "AsnId": "VGASN0829QA5450"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0824QA1080",
-            "UpdatedTimestamp": "2025-08-24T18:31:02.204",
+            "AsnId": "VGASN0829QA5450",
+            "UpdatedTimestamp": "2025-08-29T14:54:59.657",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "LpnId": "00V08242025QA60500",
+            "LpnId": "00V08292025QA29403",
             "AllocationTypeId": null,
             "BusinessUnitId": null,
             "LpnStatus": "1000",
@@ -243,7 +267,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-08-24T18:30:58.593",
+                    "CreatedTimestamp": "2025-08-29T14:54:59.435",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -254,7 +278,7 @@
                     "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "924156-365-M",
+                    "ItemId": "DD9293-100-9.5",
                     "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
@@ -269,15 +293,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "510b4a8038998b77::23ca8818abf02da5",
-                    "LpnDetailId": "0bef30f5-5dbc-4061-9f01-296702556518",
+                    "ContextId": "a567e18b7ac93933::6101f872fe141b31",
+                    "LpnDetailId": "e4e072a6-e297-4a3d-b862-159a8a75b76c",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7560602585333881188
+                        "PK": 7564792994341522236
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -289,7 +313,7 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-08-24T18:30:58.593",
+                    "UpdatedTimestamp": "2025-08-29T14:54:59.435",
                     "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
@@ -298,8 +322,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7560602585923898271",
-                    "Unique_Identifier": "7560602585923898271__0bef30f5-5dbc-4061-9f01-296702556518"
+                    "PK": "7564792994351536449",
+                    "Unique_Identifier": "7564792994351536449__e4e072a6-e297-4a3d-b862-159a8a75b76c"
                 }
             ],
             "EntityLabels": null,
@@ -311,15 +335,15 @@
             "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+            "ContextId": "a567e18b7ac93933::6101f872fe141b31",
             "Canceled": false,
-            "PK": "7560602585333881188",
-            "Unique_Identifier": "7560602585333881188__00V08242025QA60500",
+            "PK": "7564792994341522236",
+            "Unique_Identifier": "7564792994341522236__00V08292025QA29403",
             "DimensionUomId": null,
             "EstimationGroupId": null
         },
         {
-            "CreatedTimestamp": "2025-08-24T18:30:58.641",
+            "CreatedTimestamp": "2025-08-29T14:54:59.436",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
@@ -342,15 +366,15 @@
             "Width": null,
             "LpnSizeTypeId": "CARTON",
             "Asn": {
-                "AsnId": "VGASN0824QA1080"
+                "AsnId": "VGASN0829QA5450"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0824QA1080",
-            "UpdatedTimestamp": "2025-08-24T18:31:02.205",
+            "AsnId": "VGASN0829QA5450",
+            "UpdatedTimestamp": "2025-08-29T14:54:59.664",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "LpnId": "00V08242025QA58401",
+            "LpnId": "00V08292025QA56604",
             "AllocationTypeId": null,
             "BusinessUnitId": null,
             "LpnStatus": "1000",
@@ -360,7 +384,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-08-24T18:30:58.643",
+                    "CreatedTimestamp": "2025-08-29T14:54:59.437",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -371,7 +395,7 @@
                     "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "924157-417-2XL",
+                    "ItemId": "DD9293-100-9.5",
                     "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
@@ -386,15 +410,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "510b4a8038998b77::23ca8818abf02da5",
-                    "LpnDetailId": "4f571bcc-9f95-40f9-a38a-a2cd2a81f166",
+                    "ContextId": "a567e18b7ac93933::6101f872fe141b31",
+                    "LpnDetailId": "9e2558ec-969d-4a85-bf1a-7080cefc95c5",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7560602586413902897
+                        "PK": 7564792994351548453
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -406,7 +430,7 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-08-24T18:30:58.643",
+                    "UpdatedTimestamp": "2025-08-29T14:54:59.437",
                     "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
@@ -415,8 +439,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7560602586423913842",
-                    "Unique_Identifier": "7560602586423913842__4f571bcc-9f95-40f9-a38a-a2cd2a81f166"
+                    "PK": "7564792994371555548",
+                    "Unique_Identifier": "7564792994371555548__9e2558ec-969d-4a85-bf1a-7080cefc95c5"
                 }
             ],
             "EntityLabels": null,
@@ -428,15 +452,15 @@
             "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+            "ContextId": "a567e18b7ac93933::6101f872fe141b31",
             "Canceled": false,
-            "PK": "7560602586413902897",
-            "Unique_Identifier": "7560602586413902897__00V08242025QA58401",
+            "PK": "7564792994351548453",
+            "Unique_Identifier": "7564792994351548453__00V08292025QA56604",
             "DimensionUomId": null,
             "EstimationGroupId": null
         },
         {
-            "CreatedTimestamp": "2025-08-24T18:30:58.644",
+            "CreatedTimestamp": "2025-08-29T14:54:59.437",
             "VolumeUomId": null,
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
@@ -459,15 +483,15 @@
             "Width": null,
             "LpnSizeTypeId": "CARTON",
             "Asn": {
-                "AsnId": "VGASN0824QA1080"
+                "AsnId": "VGASN0829QA5450"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0824QA1080",
-            "UpdatedTimestamp": "2025-08-24T18:31:02.205",
+            "AsnId": "VGASN0829QA5450",
+            "UpdatedTimestamp": "2025-08-29T14:54:59.664",
             "MarkFor": null,
             "CreatedBy": "vgana3",
             "ParentLpnId": null,
-            "LpnId": "00V08242025QA76102",
+            "LpnId": "00V08292025QA88205",
             "AllocationTypeId": null,
             "BusinessUnitId": null,
             "LpnStatus": "1000",
@@ -477,7 +501,7 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-08-24T18:30:58.645",
+                    "CreatedTimestamp": "2025-08-29T14:54:59.438",
                     "Extended": {
                         "CutNumber": null,
                         "PurchaseOrderItemId": null,
@@ -488,7 +512,7 @@
                     "Process": "/asn/save",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "924156-836-XL",
+                    "ItemId": "DD9293-100-9.5",
                     "UpdatedBy": "vgana3",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
@@ -503,15 +527,15 @@
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
                     "PurchaseOrderId": "25050501",
-                    "ContextId": "510b4a8038998b77::23ca8818abf02da5",
-                    "LpnDetailId": "426cec57-8e3f-46f0-9c5f-4966e80719a1",
+                    "ContextId": "a567e18b7ac93933::6101f872fe141b31",
+                    "LpnDetailId": "f7e0e080-6a61-45d1-a79f-2b019ba9e319",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7560602586443921886
+                        "PK": 7564792994371567351
                     },
                     "QuantityUomId": "LPN",
                     "SeasonYear": null,
@@ -523,7 +547,7 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-08-24T18:30:58.645",
+                    "UpdatedTimestamp": "2025-08-29T14:54:59.438",
                     "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
@@ -532,8 +556,8 @@
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7560602586453931673",
-                    "Unique_Identifier": "7560602586453931673__426cec57-8e3f-46f0-9c5f-4966e80719a1"
+                    "PK": "7564792994381575712",
+                    "Unique_Identifier": "7564792994381575712__f7e0e080-6a61-45d1-a79f-2b019ba9e319"
                 }
             ],
             "EntityLabels": null,
@@ -545,47 +569,27 @@
             "PreReceiptStatusId": null,
             "SingleItemLpn": true,
             "PurchaseOrderId": "25050501",
-            "ContextId": "510b4a8038998b77::23ca8818abf02da5",
+            "ContextId": "a567e18b7ac93933::6101f872fe141b31",
             "Canceled": false,
-            "PK": "7560602586443921886",
-            "Unique_Identifier": "7560602586443921886__00V08242025QA76102",
+            "PK": "7564792994371567351",
+            "Unique_Identifier": "7564792994371567351__00V08292025QA88205",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA08242582",
+    "TrailerId": "TRLQA08292599",
     "FirstReceiptDate": null,
     "LastReceiptDate": null,
     "CarrierId": "AUPU",
     "ShippedLpns": 3.0,
-    "EstimatedVolume": 0.0,
+    "EstimatedVolume": 283439.52,
     "OriginFacilityId": "0005005401",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0824QA1080",
+    "AsnId": "VGASN0829QA5450",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-08-24T18:31:13.869",
+    "UpdatedTimestamp": "2025-08-29T14:55:14.111",
     "ReportingReceiptTypeId": null,
-    "ShipmentAsnAssociation": [
-        {
-            "ShipmentId": "900000409",
-            "UpdatedTimestamp": "2025-08-24T18:31:12.794",
-            "CreatedBy": "vgana3",
-            "CreatedTimestamp": "2025-08-24T18:31:12.794",
-            "BusinessUnitId": null,
-            "Process": "/shipmentAsnAssociation/bulkImport/",
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "UpdatedBy": "vgana3",
-            "ContextId": "821c44ea024119b7::108c773b2bfecf82",
-            "PK": "7560602727944036481",
-            "PurgeDate": null,
-            "Asn": {
-                "AsnId": "VGASN0824QA1080"
-            },
-            "AsnId": "VGASN0824QA1080",
-            "Unique_Identifier": "7560602727944036481__VGASN0824QA1080"
-        }
-    ],
+    "ShipmentAsnAssociation": [],
     "EstimatedDeliveryDate": null,
     "ReceivedLpns": 0.0,
     "EntityLabels": null,
@@ -593,9 +597,9 @@
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7560602583683873184",
+    "PK": "7564792994331515237",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7560602583683873184__VGASN0824QA1080"
+    "Unique_Identifier": "7564792994331515237__VGASN0829QA5450"
 }</t>
   </si>
 </sst>
@@ -960,11 +964,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
@@ -1045,17 +1069,14 @@
       <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -1064,16 +1085,16 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
         <v>28</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
       </c>
       <c r="P2">
         <v>24</v>
@@ -1085,16 +1106,16 @@
         <v>12</v>
       </c>
       <c r="S2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" t="s">
         <v>32</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>33</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>34</v>
-      </c>
-      <c r="V2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
@@ -1107,17 +1128,14 @@
       <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -1126,16 +1144,16 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>29</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
       </c>
       <c r="P3">
         <v>24</v>
@@ -1147,16 +1165,16 @@
         <v>12</v>
       </c>
       <c r="S3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>33</v>
       </c>
-      <c r="U3" t="s">
-        <v>34</v>
-      </c>
       <c r="V3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -1169,17 +1187,14 @@
       <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -1188,16 +1203,16 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="s">
         <v>28</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>29</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>31</v>
       </c>
       <c r="P4">
         <v>24</v>
@@ -1209,16 +1224,193 @@
         <v>12</v>
       </c>
       <c r="S4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" t="s">
         <v>32</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>33</v>
       </c>
-      <c r="U4" t="s">
-        <v>34</v>
-      </c>
       <c r="V4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>41</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5">
+        <v>24</v>
+      </c>
+      <c r="Q5">
+        <v>12</v>
+      </c>
+      <c r="R5">
+        <v>12</v>
+      </c>
+      <c r="S5" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U5" t="s">
+        <v>33</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6">
+        <v>24</v>
+      </c>
+      <c r="Q6">
+        <v>12</v>
+      </c>
+      <c r="R6">
+        <v>12</v>
+      </c>
+      <c r="S6" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" t="s">
+        <v>44</v>
+      </c>
+      <c r="U6" t="s">
+        <v>33</v>
+      </c>
+      <c r="V6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7">
+        <v>24</v>
+      </c>
+      <c r="Q7">
+        <v>12</v>
+      </c>
+      <c r="R7">
+        <v>12</v>
+      </c>
+      <c r="S7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U7" t="s">
+        <v>33</v>
+      </c>
+      <c r="V7" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1233,12 +1425,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -782,6 +782,7 @@
     "BusinessUnitId": null,
     "PreDeterminedLpnCount": 2.0,
     "AsnVerificationDate": null,
+    "TrailerPositionId": null,
     "PreReceiptStatusId": null,
     "ContextId": "2449a9d86e8392f1::f3bf62b78b2a60e8",
     "Canceled": false,
@@ -832,6 +833,7 @@
             "LpnStatus": "1000",
             "LocationId": null,
             "LpnTypeId": "ILPN",
+            "AlternatePurchaseOrderId": null,
             "LpnDetail": [
                 {
                     "ExpiryDate": null,
@@ -887,6 +889,7 @@
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
                     "ShippedQuantity": 6.0,
+                    "AlternatePurchaseOrderId": null,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",
@@ -949,6 +952,7 @@
             "LpnStatus": "1000",
             "LocationId": null,
             "LpnTypeId": "ILPN",
+            "AlternatePurchaseOrderId": null,
             "LpnDetail": [
                 {
                     "ExpiryDate": null,
@@ -1004,6 +1008,7 @@
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
                     "ShippedQuantity": 6.0,
+                    "AlternatePurchaseOrderId": null,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VGASN0903QA7970</t>
+          <t>0215055293</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -560,7 +560,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00V09032025QA48400</t>
+          <t>20251114094738000001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -570,30 +570,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>924156-365-L</t>
+          <t>343880-090-10</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>BOLQA09032579</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>PROQA09032579</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AUPU</t>
+          <t>ONEY</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -601,123 +593,23 @@
           <t>CARTON</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>12</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>TRLQA09032579</t>
-        </is>
-      </c>
+          <t>57035</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-intg-user</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2025-09-03T23:47:18.927</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>VGASN0903QA7970</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>00V09032025QA57901</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>924156-365-L</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>BOLQA09032579</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>PROQA09032579</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>CARTON</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>TRLQA09032579</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2025-09-03T23:47:18.928</t>
+          <t>2025-11-16T04:01:24.351</t>
         </is>
       </c>
     </row>
@@ -747,14 +639,14 @@
         <is>
           <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-09-03T23:47:18.925",
+    "CreatedTimestamp": "2025-11-14T18:04:36.46",
     "AsnRequestedService": [],
-    "EstimatedWeight": 0.0,
+    "EstimatedWeight": 7.308,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
         "ProNumber": null,
-        "ShipmentStart": null,
+        "ShipmentStart": "2025-11-28",
         "ShipToCustomerName": null,
         "ExpediteFlag": false,
         "SealNumber": null,
@@ -765,26 +657,26 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": null,
-        "ShipmentCreateDate": null,
+        "BolNumber": "ONEY2708261011141",
+        "ShipmentCreateDate": "2025-11-14T18:02:15",
         "SalesOrderType": null
     },
     "Process": "AsnHeaderMetricsService",
-    "ProNumber": "PROQA09032579",
+    "ProNumber": null,
     "DestinationFacilityAliasId": null,
-    "UpdatedBy": "vgana3",
+    "UpdatedBy": "nike-intg-user",
     "AsnLine": [],
-    "EstimatedReceiptDate": null,
+    "EstimatedReceiptDate": "2026-01-05T00:00:00",
     "PurgeDate": null,
     "ReferenceShipmentId": null,
-    "CreatedBy": "vgana3",
+    "CreatedBy": "nike-intg-user",
     "VerificationAttempted": false,
     "BusinessUnitId": null,
-    "PreDeterminedLpnCount": 2.0,
+    "PreDeterminedLpnCount": 1.0,
     "AsnVerificationDate": null,
     "TrailerPositionId": null,
     "PreReceiptStatusId": null,
-    "ContextId": "2449a9d86e8392f1::f3bf62b78b2a60e8",
+    "ContextId": "ac1319d79b0062a2::bcfa1a2412eecbe9",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
@@ -793,25 +685,25 @@
     "ShippedDate": null,
     "AlternateAsnId": null,
     "AsnStatus": "1000",
-    "BillOfLadingNumber": "BOLQA09032579",
+    "BillOfLadingNumber": null,
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-09-03T23:47:18.926",
-            "VolumeUomId": null,
+            "CreatedTimestamp": "2025-11-14T18:04:36.464",
+            "VolumeUomId": "CMQ",
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
             "VendorId": null,
-            "EstimatedWeight": null,
+            "EstimatedWeight": 7.308,
             "Extended": {
-                "LpnLength": 24.0,
-                "LpnHeight": 12.0,
-                "DestinationFacilityId": null,
-                "LpnWidth": 12.0
+                "LpnLength": null,
+                "LpnHeight": null,
+                "DestinationFacilityId": "1081",
+                "LpnWidth": null
             },
             "DiversionCodeId": null,
-            "Process": "/asn/save",
+            "Process": "BulkImportAsn",
             "ItemAttributesValidated": true,
-            "UpdatedBy": "vgana3",
+            "UpdatedBy": "nike-intg-user",
             "LpnRequestedService": [],
             "Height": null,
             "FinalDestinationAddress": null,
@@ -819,15 +711,15 @@
             "Width": null,
             "LpnSizeTypeId": "CARTON",
             "Asn": {
-                "AsnId": "VGASN0903QA7970"
+                "AsnId": "0215055293"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0903QA7970",
-            "UpdatedTimestamp": "2025-09-03T23:47:19.115",
+            "AsnId": "0215055293",
+            "UpdatedTimestamp": "2025-11-16T04:01:24.362",
             "MarkFor": null,
-            "CreatedBy": "vgana3",
+            "CreatedBy": "nike-intg-user",
             "ParentLpnId": null,
-            "LpnId": "00V09032025QA48400",
+            "LpnId": "20251114094738000001",
             "AllocationTypeId": null,
             "BusinessUnitId": null,
             "LpnStatus": "1000",
@@ -838,43 +730,43 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-09-03T23:47:18.927",
+                    "CreatedTimestamp": "2025-11-16T04:01:24.351",
                     "Extended": {
-                        "CutNumber": null,
+                        "CutNumber": "0175727200",
                         "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": null,
-                        "DeliveryNoteItemNumber": null
+                        "UnitOfMeasureCode": "PR",
+                        "DeliveryNoteItemNumber": "900001"
                     },
                     "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
+                    "Process": "BulkImportAsn",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "924156-365-L",
-                    "UpdatedBy": "vgana3",
+                    "ItemId": "343880-090-10",
+                    "UpdatedBy": "nike-intg-user",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
                     "InventoryAttribute3": null,
                     "InventoryAttribute4": null,
                     "PurgeDate": null,
                     "InventoryAttribute5": null,
-                    "PurchaseOrderLineId": "",
-                    "CreatedBy": "vgana3",
+                    "PurchaseOrderLineId": "00010",
+                    "CreatedBy": "nike-intg-user",
                     "BatchNumber": null,
                     "BusinessUnitId": null,
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
-                    "PurchaseOrderId": "25050501",
-                    "ContextId": "2449a9d86e8392f1::3ac9bc34890d3ae0",
-                    "LpnDetailId": "e62fc22c-6a09-401e-8f09-a1f20e63df56",
+                    "PurchaseOrderId": "3503906870",
+                    "ContextId": "11239e343c6e3054::40d19254d1d5d51f",
+                    "LpnDetailId": "b0edb2ea-1292-4d7a-bb60-d485492ea117",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7569432389263613120
+                        "PK": 7631434764648406113
                     },
-                    "QuantityUomId": "LPN",
+                    "QuantityUomId": "Units",
                     "SeasonYear": null,
                     "ManufacturingDate": null,
                     "Style": null,
@@ -884,179 +776,60 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-09-03T23:47:18.927",
+                    "UpdatedTimestamp": "2025-11-16T04:01:24.351",
                     "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 6.0,
+                    "ShippedQuantity": 18.0,
                     "AlternatePurchaseOrderId": null,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7569432389273622107",
-                    "Unique_Identifier": "7569432389273622107__e62fc22c-6a09-401e-8f09-a1f20e63df56"
+                    "PK": "7632656843515881552",
+                    "Unique_Identifier": "7632656843515881552__b0edb2ea-1292-4d7a-bb60-d485492ea117"
                 }
             ],
             "EntityLabels": null,
-            "WeightUomId": null,
+            "WeightUomId": "KG",
             "OrgId": "1081",
             "FacilityId": "1081",
-            "Volume": null,
+            "Volume": 99000.0,
             "Length": null,
             "PreReceiptStatusId": null,
             "SingleItemLpn": true,
-            "PurchaseOrderId": "25050501",
-            "ContextId": "2449a9d86e8392f1::3ac9bc34890d3ae0",
+            "PurchaseOrderId": "3503906870",
+            "ContextId": "11239e343c6e3054::40d19254d1d5d51f",
             "Canceled": false,
-            "PK": "7569432389263613120",
-            "Unique_Identifier": "7569432389263613120__00V09032025QA48400",
-            "DimensionUomId": null,
-            "EstimationGroupId": null
-        },
-        {
-            "CreatedTimestamp": "2025-09-03T23:47:18.927",
-            "VolumeUomId": null,
-            "PhysicalEntityCodeId": null,
-            "FinalDestinationFacilityId": null,
-            "VendorId": null,
-            "EstimatedWeight": null,
-            "Extended": {
-                "LpnLength": 24.0,
-                "LpnHeight": 12.0,
-                "DestinationFacilityId": null,
-                "LpnWidth": 12.0
-            },
-            "DiversionCodeId": null,
-            "Process": "/asn/save",
-            "ItemAttributesValidated": true,
-            "UpdatedBy": "vgana3",
-            "LpnRequestedService": [],
-            "Height": null,
-            "FinalDestinationAddress": null,
-            "PurgeDate": null,
-            "Width": null,
-            "LpnSizeTypeId": "CARTON",
-            "Asn": {
-                "AsnId": "VGASN0903QA7970"
-            },
-            "FacilityTimezone": "Japan",
-            "AsnId": "VGASN0903QA7970",
-            "UpdatedTimestamp": "2025-09-03T23:47:19.12",
-            "MarkFor": null,
-            "CreatedBy": "vgana3",
-            "ParentLpnId": null,
-            "LpnId": "00V09032025QA57901",
-            "AllocationTypeId": null,
-            "BusinessUnitId": null,
-            "LpnStatus": "1000",
-            "LocationId": null,
-            "LpnTypeId": "ILPN",
-            "AlternatePurchaseOrderId": null,
-            "LpnDetail": [
-                {
-                    "ExpiryDate": null,
-                    "RetailPrice": null,
-                    "CreatedTimestamp": "2025-09-03T23:47:18.928",
-                    "Extended": {
-                        "CutNumber": null,
-                        "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": null,
-                        "DeliveryNoteItemNumber": null
-                    },
-                    "CountryOfOrigin": "CN",
-                    "Process": "/asn/save",
-                    "AsnLineId": null,
-                    "InventoryTypeId": null,
-                    "ItemId": "924156-365-L",
-                    "UpdatedBy": "vgana3",
-                    "InventoryAttribute1": "01000",
-                    "InventoryAttribute2": null,
-                    "InventoryAttribute3": null,
-                    "InventoryAttribute4": null,
-                    "PurgeDate": null,
-                    "InventoryAttribute5": null,
-                    "PurchaseOrderLineId": "",
-                    "CreatedBy": "vgana3",
-                    "BatchNumber": null,
-                    "BusinessUnitId": null,
-                    "StandardPackQuantity": null,
-                    "ExternalOrderId": null,
-                    "PurchaseOrderId": "25050501",
-                    "ContextId": "2449a9d86e8392f1::3ac9bc34890d3ae0",
-                    "LpnDetailId": "b3ff9d19-d84b-4d24-af87-cc63e2d787b0",
-                    "OriginalShippingFacilityId": null,
-                    "StandardSubPackQuantity": null,
-                    "VendorId": null,
-                    "ExternalOrderLineId": null,
-                    "LpnDetailStatus": "1000",
-                    "Lpn": {
-                        "PK": 7569432389273635752
-                    },
-                    "QuantityUomId": "LPN",
-                    "SeasonYear": null,
-                    "ManufacturingDate": null,
-                    "Style": null,
-                    "ProductClass": null,
-                    "Season": null,
-                    "CrossReferenceOrderId": null,
-                    "HandlingUomQuantity": null,
-                    "TierQuantity": null,
-                    "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-09-03T23:47:18.928",
-                    "PrereceiptAllocatedQuantity": null,
-                    "LpnDetailAttribute": [],
-                    "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 6.0,
-                    "AlternatePurchaseOrderId": null,
-                    "EntityLabels": null,
-                    "ProductStatusId": null,
-                    "OrgId": "1081",
-                    "FacilityId": "1081",
-                    "PK": "7569432389283646212",
-                    "Unique_Identifier": "7569432389283646212__b3ff9d19-d84b-4d24-af87-cc63e2d787b0"
-                }
-            ],
-            "EntityLabels": null,
-            "WeightUomId": null,
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "Volume": null,
-            "Length": null,
-            "PreReceiptStatusId": null,
-            "SingleItemLpn": true,
-            "PurchaseOrderId": "25050501",
-            "ContextId": "2449a9d86e8392f1::3ac9bc34890d3ae0",
-            "Canceled": false,
-            "PK": "7569432389273635752",
-            "Unique_Identifier": "7569432389273635752__00V09032025QA57901",
+            "PK": "7631434764648406113",
+            "Unique_Identifier": "7631434764648406113__20251114094738000001",
             "DimensionUomId": null,
             "EstimationGroupId": null
         }
     ],
-    "TrailerId": "TRLQA09032579",
+    "TrailerId": null,
     "FirstReceiptDate": null,
     "LastReceiptDate": null,
-    "CarrierId": "AUPU",
-    "ShippedLpns": 2.0,
-    "EstimatedVolume": 0.0,
-    "OriginFacilityId": "0005005401",
+    "CarrierId": "ONEY",
+    "ShippedLpns": 1.0,
+    "EstimatedVolume": 99000.0,
+    "OriginFacilityId": "57035",
     "FacilityTimezone": "Japan",
-    "AsnId": "VGASN0903QA7970",
+    "AsnId": "0215055293",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-09-03T23:47:35.457",
+    "UpdatedTimestamp": "2025-11-14T18:04:47.713",
     "ReportingReceiptTypeId": null,
     "ShipmentAsnAssociation": [],
-    "EstimatedDeliveryDate": null,
+    "EstimatedDeliveryDate": "2026-01-05",
     "ReceivedLpns": 0.0,
     "EntityLabels": null,
     "RrnId": null,
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7569432389243602942",
+    "PK": "7631434764598392401",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7569432389243602942__VGASN0903QA7970"
+    "Unique_Identifier": "7631434764598392401__0215055293"
 }</t>
         </is>
       </c>

--- a/J30/Output_files/ASN_Search_Results.xlsx
+++ b/J30/Output_files/ASN_Search_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B0B74-F3F0-524D-975A-7ED9CD142B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EE0ABB-7BFE-6347-89F7-79F59F95EC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4820" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASN_Details" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>AsnId</t>
   </si>
@@ -89,7 +89,7 @@
     <t>UpdatedTimestamp</t>
   </si>
   <si>
-    <t>0215055465</t>
+    <t>0215055531</t>
   </si>
   <si>
     <t>1000</t>
@@ -98,10 +98,10 @@
     <t>P</t>
   </si>
   <si>
-    <t>20251204130906000001</t>
-  </si>
-  <si>
-    <t>706510-306-L/XL</t>
+    <t>20251214150952000001</t>
+  </si>
+  <si>
+    <t>487754-408-4</t>
   </si>
   <si>
     <t>ONEY</t>
@@ -116,34 +116,7 @@
     <t>nike-intg-user</t>
   </si>
   <si>
-    <t>2025-12-04T21:14:41.888</t>
-  </si>
-  <si>
-    <t>20251204130906000002</t>
-  </si>
-  <si>
-    <t>706510-306-S/M</t>
-  </si>
-  <si>
-    <t>2025-12-04T21:14:41.891</t>
-  </si>
-  <si>
-    <t>20251204130906000003</t>
-  </si>
-  <si>
-    <t>432997-128-13</t>
-  </si>
-  <si>
-    <t>2025-12-04T21:14:41.895</t>
-  </si>
-  <si>
-    <t>20251204130906000004</t>
-  </si>
-  <si>
-    <t>432997-128-14</t>
-  </si>
-  <si>
-    <t>2025-12-04T21:14:41.897</t>
+    <t>2025-12-14T23:11:39.633</t>
   </si>
   <si>
     <t>Raw_Payload</t>
@@ -151,17 +124,17 @@
   <si>
     <t>{
     "Messages": null,
-    "CreatedTimestamp": "2025-12-04T21:09:41.045",
+    "CreatedTimestamp": "2025-12-14T23:10:44.023",
     "AsnRequestedService": [],
-    "EstimatedWeight": 23.08,
+    "EstimatedWeight": 3.44,
     "Extended": {
         "ReturnsTrackingNumber": null,
         "MaximumLPNStatus": null,
         "ProNumber": null,
         "ShipmentStart": "2025-12-20",
         "ShipToCustomerName": null,
-        "ExpediteFlag": true,
-        "SealNumber": "SERIAL2025EC",
+        "ExpediteFlag": false,
+        "SealNumber": "SERIAL2025ZA",
         "MinimumLPNStatus": null,
         "SoldToCustomerName": null,
         "Digital": null,
@@ -169,8 +142,8 @@
         "ReturnTrackingId": null,
         "SoldToCustomerNumber": null,
         "InboundDelivery": null,
-        "BolNumber": "MAEU1512242011683",
-        "ShipmentCreateDate": "2025-12-04T21:09:06",
+        "BolNumber": "MAEU15154202581001",
+        "ShipmentCreateDate": "2025-12-14T23:09:53",
         "OriginFacilityCountryCode": "CN",
         "SalesOrderType": null
     },
@@ -185,11 +158,11 @@
     "CreatedBy": "nike-intg-user",
     "VerificationAttempted": false,
     "BusinessUnitId": null,
-    "PreDeterminedLpnCount": 4.0,
+    "PreDeterminedLpnCount": 1.0,
     "AsnVerificationDate": null,
     "TrailerPositionId": null,
     "PreReceiptStatusId": null,
-    "ContextId": "3d0bac3cc28350ab::3aeb7835a0b171cf",
+    "ContextId": "7a1b9c068659babc::523ad847c9c0636d",
     "Canceled": false,
     "AsnOriginTypeId": "P",
     "AsnLevelId": "LPN",
@@ -201,12 +174,12 @@
     "BillOfLadingNumber": null,
     "Lpn": [
         {
-            "CreatedTimestamp": "2025-12-04T21:09:41.047",
+            "CreatedTimestamp": "2025-12-14T23:10:44.085",
             "VolumeUomId": "CMQ",
             "PhysicalEntityCodeId": null,
             "FinalDestinationFacilityId": null,
             "VendorId": null,
-            "EstimatedWeight": 0.86,
+            "EstimatedWeight": 3.44,
             "Extended": {
                 "LpnLength": 23.1,
                 "LpnHeight": 12.9,
@@ -218,21 +191,21 @@
             "ItemAttributesValidated": true,
             "UpdatedBy": "nike-intg-user",
             "LpnRequestedService": [],
-            "Height": null,
+            "Height": 12.9,
             "FinalDestinationAddress": null,
             "PurgeDate": null,
-            "Width": null,
+            "Width": 20.6,
             "LpnSizeTypeId": "E75",
             "Asn": {
-                "AsnId": "0215055465"
+                "AsnId": "0215055531"
             },
             "FacilityTimezone": "Japan",
-            "AsnId": "0215055465",
-            "UpdatedTimestamp": "2025-12-04T21:14:41.928",
+            "AsnId": "0215055531",
+            "UpdatedTimestamp": "2025-12-14T23:11:39.7",
             "MarkFor": null,
             "CreatedBy": "nike-intg-user",
             "ParentLpnId": null,
-            "LpnId": "20251204130906000001",
+            "LpnId": "20251214150952000001",
             "AllocationTypeId": null,
             "BusinessUnitId": null,
             "LpnStatus": "1000",
@@ -243,18 +216,18 @@
                 {
                     "ExpiryDate": null,
                     "RetailPrice": null,
-                    "CreatedTimestamp": "2025-12-04T21:14:41.888",
+                    "CreatedTimestamp": "2025-12-14T23:11:39.633",
                     "Extended": {
-                        "CutNumber": "0175744200",
+                        "CutNumber": "0175736403",
                         "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": "EA",
-                        "DeliveryNoteItemNumber": "900002"
+                        "UnitOfMeasureCode": "PR",
+                        "DeliveryNoteItemNumber": "900001"
                     },
                     "CountryOfOrigin": "CN",
                     "Process": "BulkImportAsn",
                     "AsnLineId": null,
                     "InventoryTypeId": null,
-                    "ItemId": "706510-306-L/XL",
+                    "ItemId": "487754-408-4",
                     "UpdatedBy": "nike-intg-user",
                     "InventoryAttribute1": "01000",
                     "InventoryAttribute2": null,
@@ -268,16 +241,16 @@
                     "BusinessUnitId": null,
                     "StandardPackQuantity": null,
                     "ExternalOrderId": null,
-                    "PurchaseOrderId": "3503908581",
-                    "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-                    "LpnDetailId": "ae33a3b8-a527-47f8-9dda-00a519d4204d",
+                    "PurchaseOrderId": "3503909852",
+                    "ContextId": "b02416f21c171eaf::a89cc47ec9192f58",
+                    "LpnDetailId": "b1fc1a15-95bc-4a74-8999-432ccf00470b",
                     "OriginalShippingFacilityId": null,
                     "StandardSubPackQuantity": null,
                     "VendorId": null,
                     "ExternalOrderLineId": null,
                     "LpnDetailStatus": "1000",
                     "Lpn": {
-                        "PK": 7648825810474672667
+                        "PK": 7657538440858625672
                     },
                     "QuantityUomId": "Units",
                     "SeasonYear": null,
@@ -289,18 +262,18 @@
                     "HandlingUomQuantity": null,
                     "TierQuantity": null,
                     "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-12-04T21:14:41.888",
+                    "UpdatedTimestamp": "2025-12-14T23:11:39.633",
                     "PrereceiptAllocatedQuantity": null,
                     "LpnDetailAttribute": [],
                     "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 10.0,
+                    "ShippedQuantity": 5.0,
                     "AlternatePurchaseOrderId": null,
                     "EntityLabels": null,
                     "ProductStatusId": null,
                     "OrgId": "1081",
                     "FacilityId": "1081",
-                    "PK": "7648828818884866518",
-                    "Unique_Identifier": "7648828818884866518__ae33a3b8-a527-47f8-9dda-00a519d4204d"
+                    "PK": "7657538996338756238",
+                    "Unique_Identifier": "7657538996338756238__b1fc1a15-95bc-4a74-8999-432ccf00470b"
                 }
             ],
             "EntityLabels": null,
@@ -308,372 +281,15 @@
             "OrgId": "1081",
             "FacilityId": "1081",
             "Volume": 6138.594,
-            "Length": null,
+            "Length": 23.1,
             "PreReceiptStatusId": null,
             "SingleItemLpn": true,
-            "PurchaseOrderId": "3503908581",
-            "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
+            "PurchaseOrderId": "3503909852",
+            "ContextId": "b02416f21c171eaf::a89cc47ec9192f58",
             "Canceled": false,
-            "PK": "7648825810474672667",
-            "Unique_Identifier": "7648825810474672667__20251204130906000001",
-            "DimensionUomId": null,
-            "EstimationGroupId": null
-        },
-        {
-            "CreatedTimestamp": "2025-12-04T21:09:41.05",
-            "VolumeUomId": "CMQ",
-            "PhysicalEntityCodeId": null,
-            "FinalDestinationFacilityId": null,
-            "VendorId": null,
-            "EstimatedWeight": 0.6,
-            "Extended": {
-                "LpnLength": 23.1,
-                "LpnHeight": 12.9,
-                "DestinationFacilityId": "1081",
-                "LpnWidth": 20.6
-            },
-            "DiversionCodeId": null,
-            "Process": "BulkImportAsn",
-            "ItemAttributesValidated": true,
-            "UpdatedBy": "nike-intg-user",
-            "LpnRequestedService": [],
-            "Height": null,
-            "FinalDestinationAddress": null,
-            "PurgeDate": null,
-            "Width": null,
-            "LpnSizeTypeId": "E75",
-            "Asn": {
-                "AsnId": "0215055465"
-            },
-            "FacilityTimezone": "Japan",
-            "AsnId": "0215055465",
-            "UpdatedTimestamp": "2025-12-04T21:14:41.929",
-            "MarkFor": null,
-            "CreatedBy": "nike-intg-user",
-            "ParentLpnId": null,
-            "LpnId": "20251204130906000002",
-            "AllocationTypeId": null,
-            "BusinessUnitId": null,
-            "LpnStatus": "1000",
-            "LocationId": null,
-            "LpnTypeId": "ILPN",
-            "AlternatePurchaseOrderId": null,
-            "LpnDetail": [
-                {
-                    "ExpiryDate": null,
-                    "RetailPrice": null,
-                    "CreatedTimestamp": "2025-12-04T21:14:41.891",
-                    "Extended": {
-                        "CutNumber": "0175744200",
-                        "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": "EA",
-                        "DeliveryNoteItemNumber": "900001"
-                    },
-                    "CountryOfOrigin": "CN",
-                    "Process": "BulkImportAsn",
-                    "AsnLineId": null,
-                    "InventoryTypeId": null,
-                    "ItemId": "706510-306-S/M",
-                    "UpdatedBy": "nike-intg-user",
-                    "InventoryAttribute1": "01000",
-                    "InventoryAttribute2": null,
-                    "InventoryAttribute3": null,
-                    "InventoryAttribute4": null,
-                    "PurgeDate": null,
-                    "InventoryAttribute5": null,
-                    "PurchaseOrderLineId": "00010",
-                    "CreatedBy": "nike-intg-user",
-                    "BatchNumber": null,
-                    "BusinessUnitId": null,
-                    "StandardPackQuantity": null,
-                    "ExternalOrderId": null,
-                    "PurchaseOrderId": "3503908581",
-                    "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-                    "LpnDetailId": "7457bcc2-f617-4fab-afde-6ff703f89d08",
-                    "OriginalShippingFacilityId": null,
-                    "StandardSubPackQuantity": null,
-                    "VendorId": null,
-                    "ExternalOrderLineId": null,
-                    "LpnDetailStatus": "1000",
-                    "Lpn": {
-                        "PK": 7648825810504693627
-                    },
-                    "QuantityUomId": "Units",
-                    "SeasonYear": null,
-                    "ManufacturingDate": null,
-                    "Style": null,
-                    "ProductClass": null,
-                    "Season": null,
-                    "CrossReferenceOrderId": null,
-                    "HandlingUomQuantity": null,
-                    "TierQuantity": null,
-                    "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-12-04T21:14:41.891",
-                    "PrereceiptAllocatedQuantity": null,
-                    "LpnDetailAttribute": [],
-                    "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 10.0,
-                    "AlternatePurchaseOrderId": null,
-                    "EntityLabels": null,
-                    "ProductStatusId": null,
-                    "OrgId": "1081",
-                    "FacilityId": "1081",
-                    "PK": "7648828818914871135",
-                    "Unique_Identifier": "7648828818914871135__7457bcc2-f617-4fab-afde-6ff703f89d08"
-                }
-            ],
-            "EntityLabels": null,
-            "WeightUomId": "KG",
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "Volume": 6138.594,
-            "Length": null,
-            "PreReceiptStatusId": null,
-            "SingleItemLpn": true,
-            "PurchaseOrderId": "3503908581",
-            "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-            "Canceled": false,
-            "PK": "7648825810504693627",
-            "Unique_Identifier": "7648825810504693627__20251204130906000002",
-            "DimensionUomId": null,
-            "EstimationGroupId": null
-        },
-        {
-            "CreatedTimestamp": "2025-12-04T21:09:41.052",
-            "VolumeUomId": "CMQ",
-            "PhysicalEntityCodeId": null,
-            "FinalDestinationFacilityId": null,
-            "VendorId": null,
-            "EstimatedWeight": 10.42,
-            "Extended": {
-                "LpnLength": 23.1,
-                "LpnHeight": 12.9,
-                "DestinationFacilityId": "1081",
-                "LpnWidth": 20.6
-            },
-            "DiversionCodeId": null,
-            "Process": "BulkImportAsn",
-            "ItemAttributesValidated": true,
-            "UpdatedBy": "nike-intg-user",
-            "LpnRequestedService": [],
-            "Height": null,
-            "FinalDestinationAddress": null,
-            "PurgeDate": null,
-            "Width": null,
-            "LpnSizeTypeId": "E75",
-            "Asn": {
-                "AsnId": "0215055465"
-            },
-            "FacilityTimezone": "Japan",
-            "AsnId": "0215055465",
-            "UpdatedTimestamp": "2025-12-04T21:14:41.93",
-            "MarkFor": null,
-            "CreatedBy": "nike-intg-user",
-            "ParentLpnId": null,
-            "LpnId": "20251204130906000003",
-            "AllocationTypeId": null,
-            "BusinessUnitId": null,
-            "LpnStatus": "1000",
-            "LocationId": null,
-            "LpnTypeId": "ILPN",
-            "AlternatePurchaseOrderId": null,
-            "LpnDetail": [
-                {
-                    "ExpiryDate": null,
-                    "RetailPrice": null,
-                    "CreatedTimestamp": "2025-12-04T21:14:41.895",
-                    "Extended": {
-                        "CutNumber": "0175744201",
-                        "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": "PR",
-                        "DeliveryNoteItemNumber": "900001"
-                    },
-                    "CountryOfOrigin": "CN",
-                    "Process": "BulkImportAsn",
-                    "AsnLineId": null,
-                    "InventoryTypeId": null,
-                    "ItemId": "432997-128-13",
-                    "UpdatedBy": "nike-intg-user",
-                    "InventoryAttribute1": "01000",
-                    "InventoryAttribute2": null,
-                    "InventoryAttribute3": null,
-                    "InventoryAttribute4": null,
-                    "PurgeDate": null,
-                    "InventoryAttribute5": null,
-                    "PurchaseOrderLineId": "00010",
-                    "CreatedBy": "nike-intg-user",
-                    "BatchNumber": null,
-                    "BusinessUnitId": null,
-                    "StandardPackQuantity": null,
-                    "ExternalOrderId": null,
-                    "PurchaseOrderId": "3503908582",
-                    "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-                    "LpnDetailId": "429c23bc-e2b6-4cda-be6a-09cc330b08b2",
-                    "OriginalShippingFacilityId": null,
-                    "StandardSubPackQuantity": null,
-                    "VendorId": null,
-                    "ExternalOrderLineId": null,
-                    "LpnDetailStatus": "1000",
-                    "Lpn": {
-                        "PK": 7648825810524711433
-                    },
-                    "QuantityUomId": "Units",
-                    "SeasonYear": null,
-                    "ManufacturingDate": null,
-                    "Style": null,
-                    "ProductClass": null,
-                    "Season": null,
-                    "CrossReferenceOrderId": null,
-                    "HandlingUomQuantity": null,
-                    "TierQuantity": null,
-                    "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-12-04T21:14:41.895",
-                    "PrereceiptAllocatedQuantity": null,
-                    "LpnDetailAttribute": [],
-                    "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 10.0,
-                    "AlternatePurchaseOrderId": null,
-                    "EntityLabels": null,
-                    "ProductStatusId": null,
-                    "OrgId": "1081",
-                    "FacilityId": "1081",
-                    "PK": "7648828818944887894",
-                    "Unique_Identifier": "7648828818944887894__429c23bc-e2b6-4cda-be6a-09cc330b08b2"
-                }
-            ],
-            "EntityLabels": null,
-            "WeightUomId": "KG",
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "Volume": 6138.594,
-            "Length": null,
-            "PreReceiptStatusId": null,
-            "SingleItemLpn": true,
-            "PurchaseOrderId": "3503908582",
-            "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-            "Canceled": false,
-            "PK": "7648825810524711433",
-            "Unique_Identifier": "7648825810524711433__20251204130906000003",
-            "DimensionUomId": null,
-            "EstimationGroupId": null
-        },
-        {
-            "CreatedTimestamp": "2025-12-04T21:09:41.055",
-            "VolumeUomId": "CMQ",
-            "PhysicalEntityCodeId": null,
-            "FinalDestinationFacilityId": null,
-            "VendorId": null,
-            "EstimatedWeight": 11.2,
-            "Extended": {
-                "LpnLength": 23.1,
-                "LpnHeight": 12.9,
-                "DestinationFacilityId": "1081",
-                "LpnWidth": 20.6
-            },
-            "DiversionCodeId": null,
-            "Process": "BulkImportAsn",
-            "ItemAttributesValidated": true,
-            "UpdatedBy": "nike-intg-user",
-            "LpnRequestedService": [],
-            "Height": null,
-            "FinalDestinationAddress": null,
-            "PurgeDate": null,
-            "Width": null,
-            "LpnSizeTypeId": "E75",
-            "Asn": {
-                "AsnId": "0215055465"
-            },
-            "FacilityTimezone": "Japan",
-            "AsnId": "0215055465",
-            "UpdatedTimestamp": "2025-12-04T21:14:41.93",
-            "MarkFor": null,
-            "CreatedBy": "nike-intg-user",
-            "ParentLpnId": null,
-            "LpnId": "20251204130906000004",
-            "AllocationTypeId": null,
-            "BusinessUnitId": null,
-            "LpnStatus": "1000",
-            "LocationId": null,
-            "LpnTypeId": "ILPN",
-            "AlternatePurchaseOrderId": null,
-            "LpnDetail": [
-                {
-                    "ExpiryDate": null,
-                    "RetailPrice": null,
-                    "CreatedTimestamp": "2025-12-04T21:14:41.897",
-                    "Extended": {
-                        "CutNumber": "0175744201",
-                        "PurchaseOrderItemId": null,
-                        "UnitOfMeasureCode": "PR",
-                        "DeliveryNoteItemNumber": "900002"
-                    },
-                    "CountryOfOrigin": "CN",
-                    "Process": "BulkImportAsn",
-                    "AsnLineId": null,
-                    "InventoryTypeId": null,
-                    "ItemId": "432997-128-14",
-                    "UpdatedBy": "nike-intg-user",
-                    "InventoryAttribute1": "01000",
-                    "InventoryAttribute2": null,
-                    "InventoryAttribute3": null,
-                    "InventoryAttribute4": null,
-                    "PurgeDate": null,
-                    "InventoryAttribute5": null,
-                    "PurchaseOrderLineId": "00010",
-                    "CreatedBy": "nike-intg-user",
-                    "BatchNumber": null,
-                    "BusinessUnitId": null,
-                    "StandardPackQuantity": null,
-                    "ExternalOrderId": null,
-                    "PurchaseOrderId": "3503908582",
-                    "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-                    "LpnDetailId": "439e06f8-8ded-497b-8640-cdeab67d7526",
-                    "OriginalShippingFacilityId": null,
-                    "StandardSubPackQuantity": null,
-                    "VendorId": null,
-                    "ExternalOrderLineId": null,
-                    "LpnDetailStatus": "1000",
-                    "Lpn": {
-                        "PK": 7648825810554736147
-                    },
-                    "QuantityUomId": "Units",
-                    "SeasonYear": null,
-                    "ManufacturingDate": null,
-                    "Style": null,
-                    "ProductClass": null,
-                    "Season": null,
-                    "CrossReferenceOrderId": null,
-                    "HandlingUomQuantity": null,
-                    "TierQuantity": null,
-                    "CrossReferenceOrderLineId": null,
-                    "UpdatedTimestamp": "2025-12-04T21:14:41.897",
-                    "PrereceiptAllocatedQuantity": null,
-                    "LpnDetailAttribute": [],
-                    "LpnDetailGroupingId": null,
-                    "ShippedQuantity": 10.0,
-                    "AlternatePurchaseOrderId": null,
-                    "EntityLabels": null,
-                    "ProductStatusId": null,
-                    "OrgId": "1081",
-                    "FacilityId": "1081",
-                    "PK": "7648828818974895294",
-                    "Unique_Identifier": "7648828818974895294__439e06f8-8ded-497b-8640-cdeab67d7526"
-                }
-            ],
-            "EntityLabels": null,
-            "WeightUomId": "KG",
-            "OrgId": "1081",
-            "FacilityId": "1081",
-            "Volume": 6138.594,
-            "Length": null,
-            "PreReceiptStatusId": null,
-            "SingleItemLpn": true,
-            "PurchaseOrderId": "3503908582",
-            "ContextId": "db68c5b90fdf263a::cda82493599a8cb2",
-            "Canceled": false,
-            "PK": "7648825810554736147",
-            "Unique_Identifier": "7648825810554736147__20251204130906000004",
-            "DimensionUomId": null,
+            "PK": "7657538440858625672",
+            "Unique_Identifier": "7657538440858625672__20251214150952000001",
+            "DimensionUomId": "cm",
             "EstimationGroupId": null
         }
     ],
@@ -681,13 +297,13 @@
     "FirstReceiptDate": null,
     "LastReceiptDate": null,
     "CarrierId": "ONEY",
-    "ShippedLpns": 4.0,
-    "EstimatedVolume": 24554.376,
+    "ShippedLpns": 1.0,
+    "EstimatedVolume": 6138.594,
     "OriginFacilityId": "ASH",
     "FacilityTimezone": "Japan",
-    "AsnId": "0215055465",
+    "AsnId": "0215055531",
     "DestinationFacilityId": "1081",
-    "UpdatedTimestamp": "2025-12-04T21:09:52.873",
+    "UpdatedTimestamp": "2025-12-14T23:11:04.914",
     "ReportingReceiptTypeId": null,
     "ShipmentAsnAssociation": [],
     "EstimatedDeliveryDate": "2026-01-05",
@@ -697,9 +313,9 @@
     "OrgId": "1081",
     "FacilityId": "1081",
     "ExternalOrgId": null,
-    "PK": "7648825810454664226",
+    "PK": "7657538440228611249",
     "ReceivingCompleted": false,
-    "Unique_Identifier": "7648825810454664226__0215055465"
+    "Unique_Identifier": "7657538440228611249__0215055531"
 }</t>
   </si>
 </sst>
@@ -1064,8 +680,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -1073,7 +689,7 @@
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
@@ -1086,6 +702,7 @@
     <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="21.83203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1178,7 +795,7 @@
         <v>26</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1206,156 +823,6 @@
       </c>
       <c r="V2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3">
-        <v>23.1</v>
-      </c>
-      <c r="Q3">
-        <v>12.9</v>
-      </c>
-      <c r="R3">
-        <v>20.6</v>
-      </c>
-      <c r="S3" t="s">
-        <v>29</v>
-      </c>
-      <c r="U3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4">
-        <v>23.1</v>
-      </c>
-      <c r="Q4">
-        <v>12.9</v>
-      </c>
-      <c r="R4">
-        <v>20.6</v>
-      </c>
-      <c r="S4" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" t="s">
-        <v>30</v>
-      </c>
-      <c r="V4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5">
-        <v>23.1</v>
-      </c>
-      <c r="Q5">
-        <v>12.9</v>
-      </c>
-      <c r="R5">
-        <v>20.6</v>
-      </c>
-      <c r="S5" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1370,12 +837,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
